--- a/Testdaten/Testdaten von und für GPT-4/OpenCart-TestExecution Results_GPT-4_ausgewertet.xlsx
+++ b/Testdaten/Testdaten von und für GPT-4/OpenCart-TestExecution Results_GPT-4_ausgewertet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marvi\Desktop\Bachelor-Thesis\Testdaten\Testdaten von und für GPT-4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4DC079A-00C5-4D59-A343-4CD12D71F389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7137E4-447F-46AB-AC64-74804BC924C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="29" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Scenarios" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
     <sheet name="Gift Certificate" sheetId="27" r:id="rId27"/>
     <sheet name="Specail Offers" sheetId="28" r:id="rId28"/>
     <sheet name="Header Menu Footer Options" sheetId="29" r:id="rId29"/>
-    <sheet name="Currencies" sheetId="30" r:id="rId30"/>
+    <sheet name="Currencies" sheetId="31" r:id="rId30"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="223">
   <si>
     <t>Test Scenario Description</t>
   </si>
@@ -610,6 +610,254 @@
 P = 0,5
 R = 0,5
 F1 = 0,5</t>
+  </si>
+  <si>
+    <t>Open Login Page</t>
+  </si>
+  <si>
+    <t>1. Click on 'Login' button</t>
+  </si>
+  <si>
+    <t>Login form appears</t>
+  </si>
+  <si>
+    <t>Verify UI elements on Login Page</t>
+  </si>
+  <si>
+    <t>1. Click on 'Login' button
+2. Verify if 'Email', 'Password', 'Login' button, 'Forgot your password?', and 'Create an OpenCart account' are present</t>
+  </si>
+  <si>
+    <t>All elements should be visible and clickable</t>
+  </si>
+  <si>
+    <t>Successful Login</t>
+  </si>
+  <si>
+    <t>Valid Login</t>
+  </si>
+  <si>
+    <t>1. Click on 'Login' button
+2. Enter valid email and password
+3. Click 'Login'</t>
+  </si>
+  <si>
+    <t>User is successfully logged in</t>
+  </si>
+  <si>
+    <t>Login with Incorrect Password</t>
+  </si>
+  <si>
+    <t>Invalid Login</t>
+  </si>
+  <si>
+    <t>1. Click on 'Login' button
+2. Enter valid email and incorrect password
+3. Click 'Login'</t>
+  </si>
+  <si>
+    <t>Error message: 'No match for E-Mail and/or Password.'</t>
+  </si>
+  <si>
+    <t>Login with Unregistered Email</t>
+  </si>
+  <si>
+    <t>1. Click on 'Login' button
+2. Enter an unregistered email and any password
+3. Click 'Login'</t>
+  </si>
+  <si>
+    <t>Login with Empty Email</t>
+  </si>
+  <si>
+    <t>1. Click on 'Login' button
+2. Leave the email field empty and enter a valid password
+3. Click 'Login'</t>
+  </si>
+  <si>
+    <t>Error message displayed</t>
+  </si>
+  <si>
+    <t>Login with Empty Password</t>
+  </si>
+  <si>
+    <t>1. Click on 'Login' button
+2. Enter a valid email and leave the password field empty
+3. Click 'Login'</t>
+  </si>
+  <si>
+    <t>Login with Both Fields Empty</t>
+  </si>
+  <si>
+    <t>1. Click on 'Login' button
+2. Leave both email and password fields empty
+3. Click 'Login'</t>
+  </si>
+  <si>
+    <t>Validate Forgot Password Link</t>
+  </si>
+  <si>
+    <t>Password Recovery</t>
+  </si>
+  <si>
+    <t>1. Click on 'Login' button
+2. Click 'Forgot your password?'</t>
+  </si>
+  <si>
+    <t>User is redirected to password recovery page</t>
+  </si>
+  <si>
+    <t>Validate Navigation Back to Login</t>
+  </si>
+  <si>
+    <t>Navigation Check</t>
+  </si>
+  <si>
+    <t>1. Click on 'Login' button
+2. Click 'Forgot your password?'
+3. Click 'Login?'</t>
+  </si>
+  <si>
+    <t>User is redirected back to the login page</t>
+  </si>
+  <si>
+    <t>Password Recovery with Valid Email</t>
+  </si>
+  <si>
+    <t>1. Click on 'Login' button
+2. Click 'Forgot your password?'
+3. Enter a registered email
+4. Click 'Submit'</t>
+  </si>
+  <si>
+    <t>Password recovery email is sent</t>
+  </si>
+  <si>
+    <t>Password Recovery with Invalid Email</t>
+  </si>
+  <si>
+    <t>1. Click on 'Login' button
+2. Click 'Forgot your password?'
+3. Enter an unregistered email
+4. Click 'Submit'</t>
+  </si>
+  <si>
+    <t>Password Recovery with Empty Email Field</t>
+  </si>
+  <si>
+    <t>1. Click on 'Login' button
+2. Click 'Forgot your password?'
+3. Leave the email field empty
+4. Click 'Submit'</t>
+  </si>
+  <si>
+    <t>Timeout After 30 Minutes</t>
+  </si>
+  <si>
+    <t>Session Timeout</t>
+  </si>
+  <si>
+    <t>1. Click on 'Login' button
+2. Enter valid email and password
+3. Click 'Login'
+4. Stay inactive for 30 minutes</t>
+  </si>
+  <si>
+    <t>User is automatically logged out</t>
+  </si>
+  <si>
+    <t>Logout and Return to Login Page</t>
+  </si>
+  <si>
+    <t>Logout Verification</t>
+  </si>
+  <si>
+    <t>1. Click on 'Login' button
+2. Enter valid email and password
+3. Click 'Login'
+4. Click 'Logout'</t>
+  </si>
+  <si>
+    <t>User is logged out and redirected to the login page</t>
+  </si>
+  <si>
+    <t>Verify Password Masking</t>
+  </si>
+  <si>
+    <t>UI Check</t>
+  </si>
+  <si>
+    <t>1. Click on 'Login' button
+2. Enter any password
+3. Observe the password field</t>
+  </si>
+  <si>
+    <t>Password is masked (shown as dots or asterisks)</t>
+  </si>
+  <si>
+    <t>Verify Navigation Bar Elements</t>
+  </si>
+  <si>
+    <t>1. Click on 'Login' button
+2. Verify 'Features', 'Demo', 'Marketplace', 'Blog', 'Download', 'Resources', 'Login', and 'Register' links</t>
+  </si>
+  <si>
+    <t>Login Button Disabled Until Fields Are Filled</t>
+  </si>
+  <si>
+    <t>1. Click on 'Login' button
+2. Leave one or both fields empty
+3. Observe the 'Login' button</t>
+  </si>
+  <si>
+    <t>Login Using Enter Key</t>
+  </si>
+  <si>
+    <t>1. Click on 'Login' button
+2. Enter valid email and password
+3. Press 'Enter' instead of clicking 'Login'</t>
+  </si>
+  <si>
+    <t>Verify Redirect to Registration Page</t>
+  </si>
+  <si>
+    <t>1. Click on 'Login' button
+2. Click 'Create an OpenCart account'</t>
+  </si>
+  <si>
+    <t>User is redirected to registration page</t>
+  </si>
+  <si>
+    <t>TC021</t>
+  </si>
+  <si>
+    <t>Attempt Login After Failed Attempts</t>
+  </si>
+  <si>
+    <t>Security Check</t>
+  </si>
+  <si>
+    <t>1. Click on 'Login' button
+2. Enter incorrect credentials multiple times
+3. Try to log in with correct credentials</t>
+  </si>
+  <si>
+    <t>Check if account is locked or user can log in normally</t>
+  </si>
+  <si>
+    <t>TC022</t>
+  </si>
+  <si>
+    <t>Directly Access Secure Page Without Login</t>
+  </si>
+  <si>
+    <t>1. Open a secure page (e.g., dashboard) without logging in</t>
+  </si>
+  <si>
+    <t>User is redirected to login page</t>
+  </si>
+  <si>
+    <t>Login' button should be disabled (if implemented)</t>
   </si>
 </sst>
 </file>
@@ -714,7 +962,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -751,6 +999,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1062,6 +1316,9 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>20</v>
+      </c>
     </row>
     <row r="3" spans="1:2" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -1313,9 +1570,652 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8C1BB2C-C9A5-460D-9B77-CC0D8F3E55AC}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="21.85546875" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="19.7109375" customWidth="1"/>
+    <col min="5" max="5" width="21.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="20.85546875" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" customWidth="1"/>
+    <col min="9" max="9" width="18.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="I2" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="135" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="I3" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="I4" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="I5" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I6" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I7" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="135" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="I8" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I10" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I11" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I12" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I13" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I14" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I15" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I16" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="I17" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I18" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="I19" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I20" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="195" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="I21" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I22" s="10">
+        <f>SUM(I2:I21)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="H23" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="I23" s="8">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="H24" t="s">
+        <v>151</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1412,661 +2312,556 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2118811-6422-40EF-BD37-945B8642CF7D}">
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="25.5703125" customWidth="1"/>
+    <col min="4" max="4" width="22.42578125" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+    </row>
+    <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+    </row>
+    <row r="4" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+    </row>
+    <row r="5" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+    </row>
+    <row r="6" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+    </row>
+    <row r="7" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+    </row>
+    <row r="8" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+    </row>
+    <row r="9" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+    </row>
+    <row r="10" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+    </row>
+    <row r="11" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+    </row>
+    <row r="12" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+    </row>
+    <row r="13" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+    </row>
+    <row r="14" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+    </row>
+    <row r="15" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+    </row>
+    <row r="16" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+    </row>
+    <row r="17" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+    </row>
+    <row r="18" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+    </row>
+    <row r="19" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+    </row>
+    <row r="20" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+    </row>
+    <row r="21" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+    </row>
+    <row r="22" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+    </row>
+    <row r="23" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7665E2E6-5E9A-4EF8-B9F5-D0AC7746DA1E}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83B7116B-4DF8-4BB1-9D76-F6F969D5F7C7}">
-  <dimension ref="A1:I24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22.5703125" customWidth="1"/>
-    <col min="2" max="2" width="23.140625" customWidth="1"/>
-    <col min="3" max="3" width="24.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="5" width="21.140625" customWidth="1"/>
-    <col min="6" max="6" width="21" customWidth="1"/>
-    <col min="7" max="7" width="19.5703125" customWidth="1"/>
-    <col min="8" max="8" width="19.85546875" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="I2" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="120" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="I3" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="I4" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="120" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I5" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I6" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I7" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="120" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="I8" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I9" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I10" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I11" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I12" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="120" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I13" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I14" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I15" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I16" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="120" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I17" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="120" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I18" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="I19" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="105" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I20" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="150" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H21" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="I21" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="I22" s="10">
-        <f>SUM(I2:I21)</f>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="H23" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="I23" s="8">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="H24" t="s">
-        <v>151</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>152</v>
-      </c>
-    </row>
-  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Testdaten/Testdaten von und für GPT-4/OpenCart-TestExecution Results_GPT-4_ausgewertet.xlsx
+++ b/Testdaten/Testdaten von und für GPT-4/OpenCart-TestExecution Results_GPT-4_ausgewertet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marvi\Desktop\Bachelor-Thesis\Testdaten\Testdaten von und für GPT-4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7137E4-447F-46AB-AC64-74804BC924C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{565E8ED6-7CDE-4FDF-BEED-CDA4F0DF3832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Scenarios" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="229">
   <si>
     <t>Test Scenario Description</t>
   </si>
@@ -209,14 +209,6 @@
   </si>
   <si>
     <t>Ja</t>
-  </si>
-  <si>
-    <t>TP = 1
-FP = 0
-TN = 0
-P = 1
-R = 1
-F1 = 1</t>
   </si>
   <si>
     <t>TC002</t>
@@ -235,15 +227,6 @@
     <t>All fields and Captcha should be visible</t>
   </si>
   <si>
-    <t>TP = 1
-FP = 0
-TN = 1
-Button "Register" wird nicht gecheckt
-P = 0,5
-R = 0,5
-F1 = 0,5</t>
-  </si>
-  <si>
     <t>TC003</t>
   </si>
   <si>
@@ -258,14 +241,6 @@
   </si>
   <si>
     <t>Error messages for all required fields</t>
-  </si>
-  <si>
-    <t>TP = 2
-FP = 0
-TN = 0
-P = 1
-R = 1
-F1 = 1</t>
   </si>
   <si>
     <t>TC004</t>
@@ -287,14 +262,6 @@
     <t>Welcome message appears, verification email is sent</t>
   </si>
   <si>
-    <t>TP = 5
-FP = 0
-TN = 0
-P = 1
-R = 1
-F1 = 1</t>
-  </si>
-  <si>
     <t>TC005</t>
   </si>
   <si>
@@ -312,14 +279,6 @@
     <t>Error: 'Username is already registered'</t>
   </si>
   <si>
-    <t>TP = 3
-FP = 0
-TN = 0
-P = 1
-R = 1
-F1 = 1</t>
-  </si>
-  <si>
     <t>TC006</t>
   </si>
   <si>
@@ -352,14 +311,6 @@
   </si>
   <si>
     <t>Error message for the missing field</t>
-  </si>
-  <si>
-    <t>TP = 2
-FP = 0
-TN = 1 Es wird nicht nach First Name und Last Name gecheckt
-P = 2/3
-R = 2/3
-F1 = 2/3</t>
   </si>
   <si>
     <t>TC008</t>
@@ -552,14 +503,6 @@
     <t>Entered details should persist (if implemented)</t>
   </si>
   <si>
-    <t>TP = 4
-FP = 0
-TN = 0
-P = 1
-R = 1
-F1 = 1</t>
-  </si>
-  <si>
     <t>TC019</t>
   </si>
   <si>
@@ -602,14 +545,6 @@
   <si>
     <t>(17/27) * 100
 = 62,9%</t>
-  </si>
-  <si>
-    <t>TP = 1
-FP = 0
-TN = 1, Es wird nicht geschaut ob auch "Opencart angezeigt wird", dies ist jedoch auch in der Leiste
-P = 0,5
-R = 0,5
-F1 = 0,5</t>
   </si>
   <si>
     <t>Open Login Page</t>
@@ -858,6 +793,110 @@
   </si>
   <si>
     <t>Login' button should be disabled (if implemented)</t>
+  </si>
+  <si>
+    <t>TP = 1
+FP = 0
+FN = 0
+P = 1
+R = 1
+F1 = 1</t>
+  </si>
+  <si>
+    <t>TP = 1
+FP = 0
+FN = 1
+Button "Register" wird nicht gecheckt
+P = 1
+R = 0,5
+F1 = 0,5</t>
+  </si>
+  <si>
+    <t>TP = 2
+FP = 0
+FN = 0
+P = 1
+R = 1
+F1 = 1</t>
+  </si>
+  <si>
+    <t>TP = 5
+FP = 0
+FN = 0
+P = 1
+R = 1
+F1 = 1</t>
+  </si>
+  <si>
+    <t>TP = 3
+FP = 0
+FN = 0
+P = 1
+R = 1
+F1 = 1</t>
+  </si>
+  <si>
+    <t>TP = 2
+FP = 0
+FN = 1 Es wird nicht nach First Name und Last Name gecheckt
+P = 2/3
+R = 2/3
+F1 = 2/3</t>
+  </si>
+  <si>
+    <t>TP = 4
+FP = 0
+FN = 0
+P = 1
+R = 1
+F1 = 1</t>
+  </si>
+  <si>
+    <t>TP = 1
+FP = 0
+FN = 1, Es wird nicht geschaut ob auch "Opencart angezeigt wird", dies ist jedoch auch in der Leiste
+P = 0,5
+R = 0,5
+F1 = 0,5</t>
+  </si>
+  <si>
+    <t>Falsches Erwartetes Ergebnis, die Funktion wurde nicht implementiert und GPT-4 wusste nicht ob es implementiert ist oder nicht</t>
+  </si>
+  <si>
+    <t>TP = 1
+FP = 0
+FN = 1
+Button "Register" wird nicht gecheckt
+P = 1
+R = 0,5
+F1 = 0,66</t>
+  </si>
+  <si>
+    <t>TP = 1
+FP = 0
+FN = 1, Es wird nicht geschaut ob auch "Opencart angezeigt wird", dies ist jedoch auch in der Leiste
+P = 1
+R = 0,5
+F1 = 0,66</t>
+  </si>
+  <si>
+    <t>TP = 2
+FP = 1, Es sind nur Punkte 
+FN = 0
+P = 2/3
+R = 1
+F1 = 0,8</t>
+  </si>
+  <si>
+    <t>TP = 2
+FP = 0
+FN = 1 Es wird nicht nach First Name und Last Name gecheckt
+P = 1
+R = 2/3
+F1 = 0,8</t>
+  </si>
+  <si>
+    <t>Anzahl positive Testfälle</t>
   </si>
 </sst>
 </file>
@@ -962,7 +1001,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1000,11 +1039,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1324,6 +1360,9 @@
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>22</v>
+      </c>
     </row>
     <row r="4" spans="1:2" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -1636,7 +1675,7 @@
         <v>47</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>48</v>
+        <v>215</v>
       </c>
       <c r="I2" s="9">
         <v>1</v>
@@ -1644,28 +1683,28 @@
     </row>
     <row r="3" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>53</v>
-      </c>
       <c r="G3" s="9" t="s">
         <v>47</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>54</v>
+        <v>224</v>
       </c>
       <c r="I3" s="12">
         <v>0</v>
@@ -1673,28 +1712,28 @@
     </row>
     <row r="4" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="E4" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>59</v>
-      </c>
       <c r="G4" s="9" t="s">
         <v>47</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>60</v>
+        <v>217</v>
       </c>
       <c r="I4" s="9">
         <v>1</v>
@@ -1702,28 +1741,28 @@
     </row>
     <row r="5" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="F5" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>65</v>
-      </c>
       <c r="G5" s="9" t="s">
         <v>47</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>66</v>
+        <v>218</v>
       </c>
       <c r="I5" s="9">
         <v>1</v>
@@ -1731,28 +1770,28 @@
     </row>
     <row r="6" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>71</v>
-      </c>
       <c r="G6" s="9" t="s">
         <v>47</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>72</v>
+        <v>219</v>
       </c>
       <c r="I6" s="9">
         <v>1</v>
@@ -1760,28 +1799,28 @@
     </row>
     <row r="7" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>47</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>72</v>
+        <v>219</v>
       </c>
       <c r="I7" s="9">
         <v>1</v>
@@ -1789,28 +1828,28 @@
     </row>
     <row r="8" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>47</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>83</v>
+        <v>227</v>
       </c>
       <c r="I8" s="12">
         <v>0</v>
@@ -1818,28 +1857,28 @@
     </row>
     <row r="9" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>47</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>72</v>
+        <v>219</v>
       </c>
       <c r="I9" s="9">
         <v>1</v>
@@ -1847,28 +1886,28 @@
     </row>
     <row r="10" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>47</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>72</v>
+        <v>219</v>
       </c>
       <c r="I10" s="9">
         <v>1</v>
@@ -1876,28 +1915,28 @@
     </row>
     <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="G11" s="9" t="s">
         <v>47</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>72</v>
+        <v>219</v>
       </c>
       <c r="I11" s="9">
         <v>1</v>
@@ -1905,28 +1944,28 @@
     </row>
     <row r="12" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>47</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>72</v>
+        <v>219</v>
       </c>
       <c r="I12" s="9">
         <v>1</v>
@@ -1934,28 +1973,28 @@
     </row>
     <row r="13" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>47</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>72</v>
+        <v>219</v>
       </c>
       <c r="I13" s="9">
         <v>1</v>
@@ -1963,28 +2002,28 @@
     </row>
     <row r="14" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G14" s="9" t="s">
         <v>47</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>72</v>
+        <v>219</v>
       </c>
       <c r="I14" s="9">
         <v>1</v>
@@ -1992,28 +2031,28 @@
     </row>
     <row r="15" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>47</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>72</v>
+        <v>219</v>
       </c>
       <c r="I15" s="9">
         <v>1</v>
@@ -2021,28 +2060,28 @@
     </row>
     <row r="16" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="G16" s="9" t="s">
         <v>47</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>72</v>
+        <v>219</v>
       </c>
       <c r="I16" s="9">
         <v>1</v>
@@ -2050,28 +2089,28 @@
     </row>
     <row r="17" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="G17" s="9" t="s">
         <v>47</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>66</v>
+        <v>218</v>
       </c>
       <c r="I17" s="9">
         <v>1</v>
@@ -2079,28 +2118,28 @@
     </row>
     <row r="18" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G18" s="9" t="s">
         <v>47</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>72</v>
+        <v>219</v>
       </c>
       <c r="I18" s="9">
         <v>1</v>
@@ -2108,28 +2147,28 @@
     </row>
     <row r="19" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="G19" s="9" t="s">
         <v>47</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>139</v>
+        <v>221</v>
       </c>
       <c r="I19" s="9">
         <v>1</v>
@@ -2137,28 +2176,28 @@
     </row>
     <row r="20" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>47</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>72</v>
+        <v>219</v>
       </c>
       <c r="I20" s="9">
         <v>1</v>
@@ -2166,34 +2205,37 @@
     </row>
     <row r="21" spans="1:9" ht="195" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>47</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>153</v>
+        <v>225</v>
       </c>
       <c r="I21" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="H22" s="11" t="s">
+        <v>228</v>
+      </c>
       <c r="I22" s="10">
         <f>SUM(I2:I21)</f>
         <v>17</v>
@@ -2201,7 +2243,7 @@
     </row>
     <row r="23" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="H23" s="11" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="I23" s="8">
         <v>27</v>
@@ -2209,10 +2251,10 @@
     </row>
     <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H24" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -2312,7 +2354,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2118811-6422-40EF-BD37-945B8642CF7D}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -2321,536 +2363,702 @@
     <col min="4" max="4" width="22.42578125" customWidth="1"/>
     <col min="5" max="5" width="24.28515625" customWidth="1"/>
     <col min="6" max="6" width="22.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="8" max="8" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="G1" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="I2" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="I3" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="E2" s="11" t="s">
+      <c r="F4" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="G4" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="I4" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-    </row>
-    <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B3" s="11" t="s">
+      <c r="C5" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" s="11" t="s">
+      <c r="E5" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F5" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-    </row>
-    <row r="4" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="11" t="s">
+      <c r="G5" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="I5" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" s="11" t="s">
+      <c r="C6" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="F6" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="I6" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="C7" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-    </row>
-    <row r="5" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" s="11" t="s">
+      <c r="F7" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="11" t="s">
+      <c r="G7" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="I7" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="C8" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F8" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="I8" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-    </row>
-    <row r="6" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="11" t="s">
+      <c r="C9" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="E6" s="11" t="s">
+      <c r="F9" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="I9" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="F6" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-    </row>
-    <row r="7" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" s="11" t="s">
+      <c r="C10" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="E7" s="11" t="s">
+      <c r="E10" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F10" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-    </row>
-    <row r="8" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B8" s="11" t="s">
+      <c r="G10" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="I10" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="E8" s="11" t="s">
+      <c r="C11" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="F8" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-    </row>
-    <row r="9" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="B9" s="11" t="s">
+      <c r="E11" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C9" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="E9" s="11" t="s">
+      <c r="F11" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-    </row>
-    <row r="10" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="B10" s="11" t="s">
+      <c r="G11" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="I11" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="11" t="s">
+      <c r="C12" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="F12" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="G12" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="I12" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-    </row>
-    <row r="11" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="B11" s="11" t="s">
+      <c r="C13" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="C11" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="11" t="s">
+      <c r="F13" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="I13" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="C14" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="E14" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F14" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="I14" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-    </row>
-    <row r="12" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B12" s="11" t="s">
+      <c r="C15" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="C12" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="E12" s="11" t="s">
+      <c r="E15" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F15" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-    </row>
-    <row r="13" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="B13" s="11" t="s">
+      <c r="G15" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="I15" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="C13" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="E13" s="11" t="s">
+      <c r="C16" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-    </row>
-    <row r="14" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="B14" s="11" t="s">
+      <c r="E16" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="C14" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="E14" s="11" t="s">
+      <c r="F16" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="F14" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-    </row>
-    <row r="15" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="B15" s="11" t="s">
+      <c r="G16" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="I16" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="C15" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="11" t="s">
+      <c r="C17" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E17" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F17" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-    </row>
-    <row r="16" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B16" s="11" t="s">
+      <c r="G17" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="I17" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="150" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="C16" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="11" t="s">
+      <c r="C18" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="F18" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="I18" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B19" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="C19" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-    </row>
-    <row r="17" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="B17" s="11" t="s">
+      <c r="F19" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="I19" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="C17" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" s="11" t="s">
+      <c r="C20" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="E20" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="F20" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="I20" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="C21" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E21" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-    </row>
-    <row r="18" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="B18" s="11" t="s">
+      <c r="F21" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="C18" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="E18" s="11" t="s">
+      <c r="G21" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="I21" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="F18" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-    </row>
-    <row r="19" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="B19" s="11" t="s">
+      <c r="B22" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="C19" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="E19" s="11" t="s">
+      <c r="C22" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="F19" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-    </row>
-    <row r="20" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="B20" s="11" t="s">
+      <c r="E22" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="C20" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="E20" s="11" t="s">
+      <c r="F22" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="F20" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-    </row>
-    <row r="21" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="B21" s="11" t="s">
+      <c r="G22" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="I22" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="C21" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="E21" s="11" t="s">
+      <c r="B23" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="C23" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="E23" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-    </row>
-    <row r="22" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
+      <c r="F23" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="B22" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D22" s="11" t="s">
+      <c r="G23" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H23" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="E22" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-    </row>
-    <row r="23" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
+      <c r="I23" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="G24" s="11"/>
+      <c r="H24" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="I24" s="8">
+        <f>SUM(I2:I23)</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="G25" s="11"/>
+      <c r="H25" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="I25" s="8">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G26" s="11"/>
+      <c r="H26" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="I26" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/Testdaten/Testdaten von und für GPT-4/OpenCart-TestExecution Results_GPT-4_ausgewertet.xlsx
+++ b/Testdaten/Testdaten von und für GPT-4/OpenCart-TestExecution Results_GPT-4_ausgewertet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marvi\Desktop\Bachelor-Thesis\Testdaten\Testdaten von und für GPT-4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{565E8ED6-7CDE-4FDF-BEED-CDA4F0DF3832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9920EF6-FBAC-41B4-87B3-52DC6F1FED50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,33 +16,34 @@
     <sheet name="Test Scenarios" sheetId="1" r:id="rId1"/>
     <sheet name="Register" sheetId="2" r:id="rId2"/>
     <sheet name="Login" sheetId="3" r:id="rId3"/>
-    <sheet name="Forgot Password" sheetId="4" r:id="rId4"/>
-    <sheet name="Search" sheetId="5" r:id="rId5"/>
-    <sheet name="Product Display Page" sheetId="6" r:id="rId6"/>
-    <sheet name="Add to Cart" sheetId="7" r:id="rId7"/>
-    <sheet name="Wish List" sheetId="8" r:id="rId8"/>
-    <sheet name="Shopping Cart" sheetId="9" r:id="rId9"/>
-    <sheet name="Home Page" sheetId="10" r:id="rId10"/>
-    <sheet name="Checkout" sheetId="11" r:id="rId11"/>
-    <sheet name="My Account" sheetId="12" r:id="rId12"/>
-    <sheet name="My Account Information" sheetId="13" r:id="rId13"/>
-    <sheet name="Change Password" sheetId="14" r:id="rId14"/>
-    <sheet name="Address Book" sheetId="15" r:id="rId15"/>
-    <sheet name="Order History" sheetId="16" r:id="rId16"/>
-    <sheet name="Order Information" sheetId="17" r:id="rId17"/>
-    <sheet name="Product Returns" sheetId="18" r:id="rId18"/>
-    <sheet name="Downloads" sheetId="19" r:id="rId19"/>
-    <sheet name="Reward Points" sheetId="20" r:id="rId20"/>
-    <sheet name="Returns" sheetId="21" r:id="rId21"/>
-    <sheet name="Transactions" sheetId="22" r:id="rId22"/>
-    <sheet name="Recurring Payments" sheetId="23" r:id="rId23"/>
-    <sheet name="Affiliate" sheetId="24" r:id="rId24"/>
-    <sheet name="Newsletter" sheetId="25" r:id="rId25"/>
-    <sheet name="Contact Us" sheetId="26" r:id="rId26"/>
-    <sheet name="Gift Certificate" sheetId="27" r:id="rId27"/>
-    <sheet name="Specail Offers" sheetId="28" r:id="rId28"/>
-    <sheet name="Header Menu Footer Options" sheetId="29" r:id="rId29"/>
-    <sheet name="Currencies" sheetId="31" r:id="rId30"/>
+    <sheet name="Logout" sheetId="32" r:id="rId4"/>
+    <sheet name="Forgot Password" sheetId="4" r:id="rId5"/>
+    <sheet name="Search" sheetId="5" r:id="rId6"/>
+    <sheet name="Product Display Page" sheetId="6" r:id="rId7"/>
+    <sheet name="Add to Cart" sheetId="7" r:id="rId8"/>
+    <sheet name="Wish List" sheetId="8" r:id="rId9"/>
+    <sheet name="Shopping Cart" sheetId="9" r:id="rId10"/>
+    <sheet name="Home Page" sheetId="10" r:id="rId11"/>
+    <sheet name="Checkout" sheetId="11" r:id="rId12"/>
+    <sheet name="My Account" sheetId="12" r:id="rId13"/>
+    <sheet name="My Account Information" sheetId="13" r:id="rId14"/>
+    <sheet name="Change Password" sheetId="14" r:id="rId15"/>
+    <sheet name="Address Book" sheetId="15" r:id="rId16"/>
+    <sheet name="Order History" sheetId="16" r:id="rId17"/>
+    <sheet name="Order Information" sheetId="17" r:id="rId18"/>
+    <sheet name="Product Returns" sheetId="18" r:id="rId19"/>
+    <sheet name="Downloads" sheetId="19" r:id="rId20"/>
+    <sheet name="Reward Points" sheetId="20" r:id="rId21"/>
+    <sheet name="Returns" sheetId="21" r:id="rId22"/>
+    <sheet name="Transactions" sheetId="22" r:id="rId23"/>
+    <sheet name="Recurring Payments" sheetId="23" r:id="rId24"/>
+    <sheet name="Affiliate" sheetId="24" r:id="rId25"/>
+    <sheet name="Newsletter" sheetId="25" r:id="rId26"/>
+    <sheet name="Contact Us" sheetId="26" r:id="rId27"/>
+    <sheet name="Gift Certificate" sheetId="27" r:id="rId28"/>
+    <sheet name="Specail Offers" sheetId="28" r:id="rId29"/>
+    <sheet name="Header Menu Footer Options" sheetId="29" r:id="rId30"/>
+    <sheet name="Currencies" sheetId="31" r:id="rId31"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -65,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="265">
   <si>
     <t>Test Scenario Description</t>
   </si>
@@ -803,15 +804,6 @@
 F1 = 1</t>
   </si>
   <si>
-    <t>TP = 1
-FP = 0
-FN = 1
-Button "Register" wird nicht gecheckt
-P = 1
-R = 0,5
-F1 = 0,5</t>
-  </si>
-  <si>
     <t>TP = 2
 FP = 0
 FN = 0
@@ -836,28 +828,12 @@
 F1 = 1</t>
   </si>
   <si>
-    <t>TP = 2
-FP = 0
-FN = 1 Es wird nicht nach First Name und Last Name gecheckt
-P = 2/3
-R = 2/3
-F1 = 2/3</t>
-  </si>
-  <si>
     <t>TP = 4
 FP = 0
 FN = 0
 P = 1
 R = 1
 F1 = 1</t>
-  </si>
-  <si>
-    <t>TP = 1
-FP = 0
-FN = 1, Es wird nicht geschaut ob auch "Opencart angezeigt wird", dies ist jedoch auch in der Leiste
-P = 0,5
-R = 0,5
-F1 = 0,5</t>
   </si>
   <si>
     <t>Falsches Erwartetes Ergebnis, die Funktion wurde nicht implementiert und GPT-4 wusste nicht ob es implementiert ist oder nicht</t>
@@ -897,6 +873,134 @@
   </si>
   <si>
     <t>Anzahl positive Testfälle</t>
+  </si>
+  <si>
+    <t>Successful Logout</t>
+  </si>
+  <si>
+    <t>Open OpenCart.com, User is logged into OpenCart account</t>
+  </si>
+  <si>
+    <t>Valid Logout</t>
+  </si>
+  <si>
+    <t>1. Click on 'Logout' button</t>
+  </si>
+  <si>
+    <t>User is redirected to the homepage, Login/Register buttons are visible</t>
+  </si>
+  <si>
+    <t>Verify UI elements after Logout</t>
+  </si>
+  <si>
+    <t>UI Verification</t>
+  </si>
+  <si>
+    <t>1. Click on 'Logout' button
+2. Verify if 'Login' and 'Register' buttons appear in the navigation bar</t>
+  </si>
+  <si>
+    <t>Navigation elements should be updated, Account-related options should disappear</t>
+  </si>
+  <si>
+    <t>Logout and Attempt to Access Account Page</t>
+  </si>
+  <si>
+    <t>1. Click on 'Logout' button
+2. Try to access the 'Account' page directly</t>
+  </si>
+  <si>
+    <t>User is redirected to the login page</t>
+  </si>
+  <si>
+    <t>Logout and Browser Back Navigation</t>
+  </si>
+  <si>
+    <t>1. Click on 'Logout' button
+2. Press the browser 'Back' button</t>
+  </si>
+  <si>
+    <t>User should not be able to access the previous session, redirected to login page</t>
+  </si>
+  <si>
+    <t>Logout and Attempt to Access Secure Page via URL</t>
+  </si>
+  <si>
+    <t>1. Click on 'Logout' button
+2. Open a secure page (e.g., dashboard) via URL</t>
+  </si>
+  <si>
+    <t>Logout During Active Session on Another Page</t>
+  </si>
+  <si>
+    <t>Session Management</t>
+  </si>
+  <si>
+    <t>1. Navigate to another section (e.g., Purchases)
+2. Click on 'Logout' button</t>
+  </si>
+  <si>
+    <t>User is logged out across all active sessions</t>
+  </si>
+  <si>
+    <t>Automatic Logout After Inactivity</t>
+  </si>
+  <si>
+    <t>Timeout Scenario</t>
+  </si>
+  <si>
+    <t>1. Stay inactive for 30 minutes
+2. Try to perform any action</t>
+  </si>
+  <si>
+    <t>User is automatically logged out and redirected to the login page</t>
+  </si>
+  <si>
+    <t>Logout and Immediate Login Attempt</t>
+  </si>
+  <si>
+    <t>Login Verification</t>
+  </si>
+  <si>
+    <t>1. Click on 'Logout' button
+2. Click 'Login' and enter credentials</t>
+  </si>
+  <si>
+    <t>User should be able to log in again successfully</t>
+  </si>
+  <si>
+    <t>Verify Logout Button Visibility</t>
+  </si>
+  <si>
+    <t>1. Click on 'Logout' button
+2. Check if 'Logout' button disappears from the navigation bar</t>
+  </si>
+  <si>
+    <t>Logout' button should not be visible after logout</t>
+  </si>
+  <si>
+    <t>Logout and Refresh the Page</t>
+  </si>
+  <si>
+    <t>1. Click on 'Logout' button
+2. Refresh the browser page</t>
+  </si>
+  <si>
+    <t>User should remain logged out, Login/Register buttons remain visible</t>
+  </si>
+  <si>
+    <t>Nicht spezifisch, was ist mit Account related Options gemeint</t>
+  </si>
+  <si>
+    <t>(19/23)*100
+= 82,6%</t>
+  </si>
+  <si>
+    <t>(9/11)*100
+= 81,8%</t>
+  </si>
+  <si>
+    <t>Test Scenario Descripton von Pavankumar21github [2022]</t>
   </si>
 </sst>
 </file>
@@ -1001,7 +1105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1040,6 +1144,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1333,22 +1452,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="74.28515625" customWidth="1"/>
     <col min="2" max="2" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="36" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="36" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1356,7 +1478,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -1364,67 +1486,70 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="36" x14ac:dyDescent="0.25">
+      <c r="B4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="36" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="36" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="36" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="36" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="36" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="36" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="36" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="36" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="36" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="36" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="36" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -1518,6 +1643,15 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69D18EF4-CB07-482B-8120-500AFEA41AAD}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F59ECDB-6887-412D-AE40-CAEFBBF69F30}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1526,7 +1660,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E3281B2-ECE2-4229-8E21-DD0154D6B597}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1535,7 +1669,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC891B4D-CEB7-428C-AF11-DCFCD005A99F}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1544,7 +1678,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67FE3611-CBBC-427E-B012-E6C8579C6CA3}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1553,7 +1687,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74085656-08C1-43DA-983A-046601A87472}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1562,7 +1696,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{884EF907-734D-47C2-A462-0A7DDD7773AA}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1571,7 +1705,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8E5B671-0B83-466E-B4C9-A5B4C2F32FB0}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1580,7 +1714,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAAF1EEB-08B3-4462-A935-285A740C21B1}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1589,17 +1723,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB318571-7AA6-48E7-8B34-1554E4D4D71F}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6366D9F1-B0C3-4E0E-A154-D57D8B3B5093}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -1704,7 +1829,7 @@
         <v>47</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I3" s="12">
         <v>0</v>
@@ -1733,7 +1858,7 @@
         <v>47</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I4" s="9">
         <v>1</v>
@@ -1762,7 +1887,7 @@
         <v>47</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I5" s="9">
         <v>1</v>
@@ -1791,7 +1916,7 @@
         <v>47</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I6" s="9">
         <v>1</v>
@@ -1820,7 +1945,7 @@
         <v>47</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I7" s="9">
         <v>1</v>
@@ -1849,7 +1974,7 @@
         <v>47</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I8" s="12">
         <v>0</v>
@@ -1878,7 +2003,7 @@
         <v>47</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I9" s="9">
         <v>1</v>
@@ -1907,7 +2032,7 @@
         <v>47</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I10" s="9">
         <v>1</v>
@@ -1936,7 +2061,7 @@
         <v>47</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I11" s="9">
         <v>1</v>
@@ -1965,7 +2090,7 @@
         <v>47</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I12" s="9">
         <v>1</v>
@@ -1994,7 +2119,7 @@
         <v>47</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I13" s="9">
         <v>1</v>
@@ -2023,7 +2148,7 @@
         <v>47</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I14" s="9">
         <v>1</v>
@@ -2052,7 +2177,7 @@
         <v>47</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I15" s="9">
         <v>1</v>
@@ -2081,7 +2206,7 @@
         <v>47</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I16" s="9">
         <v>1</v>
@@ -2110,7 +2235,7 @@
         <v>47</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I17" s="9">
         <v>1</v>
@@ -2139,7 +2264,7 @@
         <v>47</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I18" s="9">
         <v>1</v>
@@ -2168,7 +2293,7 @@
         <v>47</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I19" s="9">
         <v>1</v>
@@ -2197,7 +2322,7 @@
         <v>47</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I20" s="9">
         <v>1</v>
@@ -2226,7 +2351,7 @@
         <v>47</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I21" s="12">
         <v>0</v>
@@ -2234,7 +2359,7 @@
     </row>
     <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H22" s="11" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I22" s="10">
         <f>SUM(I2:I21)</f>
@@ -2263,6 +2388,15 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6366D9F1-B0C3-4E0E-A154-D57D8B3B5093}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBD04566-2B9F-4B07-AA34-BF57464EB60D}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2271,7 +2405,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E879D26-DF42-416A-B355-648FF3505B03}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2280,7 +2414,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2166216-EEEF-4E1B-B517-FAF39C77E32F}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2289,7 +2423,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3BDDD2-D55F-46D4-BF02-5AC4E8168912}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2298,7 +2432,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51240DEB-4720-4744-A3E5-ABE3B15218B8}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2307,7 +2441,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F321C8C-3303-4D7C-9741-9B98D2CB30B9}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2316,7 +2450,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D0881DA-FFFD-4EA2-A7CE-6EEFF29BDA2D}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2325,7 +2459,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C6C93B5-A0D8-4D55-82E6-2C662B74A26E}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2334,17 +2468,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62A08BA0-82AB-40C6-AB10-9C065EBEE794}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADC3A216-5155-4CEF-8A20-6800539D6F36}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2448,7 +2573,7 @@
         <v>47</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I3" s="9">
         <v>1</v>
@@ -2477,7 +2602,7 @@
         <v>47</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I4" s="9">
         <v>1</v>
@@ -2506,7 +2631,7 @@
         <v>47</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I5" s="9">
         <v>1</v>
@@ -2535,7 +2660,7 @@
         <v>47</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I6" s="9">
         <v>1</v>
@@ -2564,7 +2689,7 @@
         <v>47</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I7" s="9">
         <v>1</v>
@@ -2593,7 +2718,7 @@
         <v>47</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I8" s="9">
         <v>1</v>
@@ -2622,7 +2747,7 @@
         <v>47</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I9" s="9">
         <v>1</v>
@@ -2651,7 +2776,7 @@
         <v>47</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I10" s="9">
         <v>1</v>
@@ -2680,7 +2805,7 @@
         <v>47</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I11" s="9">
         <v>1</v>
@@ -2709,7 +2834,7 @@
         <v>47</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I12" s="9">
         <v>1</v>
@@ -2738,7 +2863,7 @@
         <v>47</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I13" s="9">
         <v>1</v>
@@ -2767,7 +2892,7 @@
         <v>47</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I14" s="9">
         <v>1</v>
@@ -2796,7 +2921,7 @@
         <v>47</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I15" s="9">
         <v>1</v>
@@ -2825,7 +2950,7 @@
         <v>47</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I16" s="9">
         <v>1</v>
@@ -2854,7 +2979,7 @@
         <v>47</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I17" s="12">
         <v>0</v>
@@ -2883,7 +3008,7 @@
         <v>47</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I18" s="12">
         <v>0</v>
@@ -2912,7 +3037,7 @@
         <v>47</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I19" s="12">
         <v>0</v>
@@ -2941,7 +3066,7 @@
         <v>47</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I20" s="9">
         <v>1</v>
@@ -2970,7 +3095,7 @@
         <v>47</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I21" s="9">
         <v>1</v>
@@ -2999,7 +3124,7 @@
         <v>47</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I22" s="9">
         <v>1</v>
@@ -3037,7 +3162,7 @@
     <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G24" s="11"/>
       <c r="H24" s="8" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I24" s="8">
         <f>SUM(I2:I23)</f>
@@ -3053,12 +3178,14 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G26" s="11"/>
       <c r="H26" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="I26" s="8"/>
+      <c r="I26" s="18" t="s">
+        <v>262</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -3066,6 +3193,15 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADC3A216-5155-4CEF-8A20-6800539D6F36}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7665E2E6-5E9A-4EF8-B9F5-D0AC7746DA1E}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3075,6 +3211,372 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B7DE15C-C066-406E-B74C-BED277819CA1}">
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+    <col min="4" max="4" width="19.5703125" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" customWidth="1"/>
+    <col min="8" max="8" width="17.85546875" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="I2" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="I3" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="I4" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="I5" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="I6" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="I7" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="I8" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="I9" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="I10" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="I11" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="G12" s="8"/>
+      <c r="H12" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="I12" s="8">
+        <f>SUM(I2:I11)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="H13" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="I13" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="H14" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>263</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B87FF5BC-0666-433A-9ADB-FC60B68CC696}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3083,7 +3585,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACCF51F9-3319-459B-87DB-F023A541C9C3}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3092,7 +3594,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF293EA0-B5E7-4CA4-88EA-BB5093B9A174}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3101,7 +3603,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8819886F-B11A-44ED-87B0-0DB3C124ED3B}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3110,20 +3612,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0C77B75-3DB4-41BB-A87D-FCE0B7306371}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69D18EF4-CB07-482B-8120-500AFEA41AAD}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Testdaten/Testdaten von und für GPT-4/OpenCart-TestExecution Results_GPT-4_ausgewertet.xlsx
+++ b/Testdaten/Testdaten von und für GPT-4/OpenCart-TestExecution Results_GPT-4_ausgewertet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marvi\Desktop\Bachelor-Thesis\Testdaten\Testdaten von und für GPT-4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9920EF6-FBAC-41B4-87B3-52DC6F1FED50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8901C523-13D3-469C-ADEA-9FBF523136E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Scenarios" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="345">
   <si>
     <t>Test Scenario Description</t>
   </si>
@@ -992,15 +992,287 @@
     <t>Nicht spezifisch, was ist mit Account related Options gemeint</t>
   </si>
   <si>
-    <t>(19/23)*100
-= 82,6%</t>
-  </si>
-  <si>
     <t>(9/11)*100
 = 81,8%</t>
   </si>
   <si>
     <t>Test Scenario Descripton von Pavankumar21github [2022]</t>
+  </si>
+  <si>
+    <t>Request Password Reset with Valid Email</t>
+  </si>
+  <si>
+    <t>Open OpenCart.com, User is on the 'Forgot Password' page, An existing account is required</t>
+  </si>
+  <si>
+    <t>Valid Reset Request</t>
+  </si>
+  <si>
+    <t>1. Click on 'Forgotten Password' link from Login page
+2. Enter a registered email
+3. Click 'Submit'</t>
+  </si>
+  <si>
+    <t>Success message: 'An email with a reset link has been sent'</t>
+  </si>
+  <si>
+    <t>Request Password Reset with Unregistered Email</t>
+  </si>
+  <si>
+    <t>Open OpenCart.com, User is on the 'Forgot Password' page</t>
+  </si>
+  <si>
+    <t>Invalid Reset Request</t>
+  </si>
+  <si>
+    <t>1. Click on 'Forgotten Password' link from Login page
+2. Enter an unregistered email
+3. Click 'Submit'</t>
+  </si>
+  <si>
+    <t>Error message: 'E-Mail Address does not appear to be valid!'</t>
+  </si>
+  <si>
+    <t>Request Password Reset with Empty Email Field</t>
+  </si>
+  <si>
+    <t>1. Click on 'Forgotten Password' link from Login page
+2. Leave the email field empty
+3. Click 'Submit'</t>
+  </si>
+  <si>
+    <t>Access Password Reset Link</t>
+  </si>
+  <si>
+    <t>Open OpenCart.com, User has received the password reset email, An existing account is required</t>
+  </si>
+  <si>
+    <t>Verify Reset Link</t>
+  </si>
+  <si>
+    <t>1. Click on the password reset link in the email</t>
+  </si>
+  <si>
+    <t>User is redirected to the 'Reset Password' page</t>
+  </si>
+  <si>
+    <t>Attempt to Use Expired Password Reset Link</t>
+  </si>
+  <si>
+    <t>Invalid Reset Link</t>
+  </si>
+  <si>
+    <t>1. Click on an expired reset link</t>
+  </si>
+  <si>
+    <t>Error message: 'The password reset link has expired!'</t>
+  </si>
+  <si>
+    <t>Reset Password with Matching New Passwords</t>
+  </si>
+  <si>
+    <t>Open OpenCart.com, User is on the 'Reset Password' page, User has received the password reset email, An existing account is required</t>
+  </si>
+  <si>
+    <t>Valid Password Reset</t>
+  </si>
+  <si>
+    <t>1. Click on 'Forgotten Password' link from Login page
+2. Enter a new valid password
+3. Re-enter the same password
+4. Click 'Continue'</t>
+  </si>
+  <si>
+    <t>Success message: 'Your password has been updated'</t>
+  </si>
+  <si>
+    <t>Reset Password with Non-Matching Confirmation</t>
+  </si>
+  <si>
+    <t>Invalid Password Reset</t>
+  </si>
+  <si>
+    <t>1. Click on 'Forgotten Password' link from Login page
+2. Enter a new password
+3. Enter a different confirmation password
+4. Click 'Continue'</t>
+  </si>
+  <si>
+    <t>Error message: 'Passwords do not match!'</t>
+  </si>
+  <si>
+    <t>Reset Password with Weak Password</t>
+  </si>
+  <si>
+    <t>1. Click on 'Forgotten Password' link from Login page
+2. Enter a weak password (e.g., too short)
+3. Enter the same confirmation password
+4. Click 'Continue'</t>
+  </si>
+  <si>
+    <t>Error message: 'Password does not meet security requirements!'</t>
+  </si>
+  <si>
+    <t>Reset Password with Empty Fields</t>
+  </si>
+  <si>
+    <t>1. Click on 'Forgotten Password' link from Login page
+2. Leave both password fields empty
+3. Click 'Continue'</t>
+  </si>
+  <si>
+    <t>Error message: 'Password fields cannot be empty!'</t>
+  </si>
+  <si>
+    <t>Login After Successful Password Reset</t>
+  </si>
+  <si>
+    <t>Verify New Password</t>
+  </si>
+  <si>
+    <t>1. Enter email and new password on the login page
+2. Click 'Login'</t>
+  </si>
+  <si>
+    <t>UI Verification of Password Reset Page</t>
+  </si>
+  <si>
+    <t>1. Verify presence of 'E-Mail Address' field
+2. Verify 'Submit' button is visible</t>
+  </si>
+  <si>
+    <t>All UI elements should be visible and functional</t>
+  </si>
+  <si>
+    <t>UI Verification of Reset Password Page</t>
+  </si>
+  <si>
+    <t>Open OpenCart.com, User is on the 'Reset Password' page, User has received the password reset email</t>
+  </si>
+  <si>
+    <t>1. Click on 'Forgotten Password' link from Login page
+2. Verify presence of 'Password' and 'Confirm Password' fields
+3. Verify 'Continue' button is visible</t>
+  </si>
+  <si>
+    <t>Verify Navigation Back to Login Page</t>
+  </si>
+  <si>
+    <t>1. Click on 'Login?' link</t>
+  </si>
+  <si>
+    <t>Request Another Password Reset Without Waiting</t>
+  </si>
+  <si>
+    <t>Reset Request Spam Check</t>
+  </si>
+  <si>
+    <t>1. Enter a registered email
+2. Click 'Submit' twice in quick succession</t>
+  </si>
+  <si>
+    <t>Verify if multiple reset emails are sent or system blocks rapid requests</t>
+  </si>
+  <si>
+    <t>Verify Logout After Password Reset</t>
+  </si>
+  <si>
+    <t>1. Complete password reset
+2. Try to use old password to log in</t>
+  </si>
+  <si>
+    <t>Old password should no longer work</t>
+  </si>
+  <si>
+    <t>Attempt to Use Reset Link After Password Change</t>
+  </si>
+  <si>
+    <t>1. Change password successfully
+2. Try to use the old reset link</t>
+  </si>
+  <si>
+    <t>Reset Password and Attempt Old Password Login</t>
+  </si>
+  <si>
+    <t>1. Click on 'Forgotten Password' link from Login page
+2. Change password successfully
+3. Try to log in with the old password</t>
+  </si>
+  <si>
+    <t>Old password should not work, only new password is valid</t>
+  </si>
+  <si>
+    <t>Verify Reset Email Not Received Due to Incorrect Address</t>
+  </si>
+  <si>
+    <t>Email Delivery Check</t>
+  </si>
+  <si>
+    <t>1. Enter a wrongly formatted email
+2. Click 'Submit'</t>
+  </si>
+  <si>
+    <t>Verify Password Field Masking</t>
+  </si>
+  <si>
+    <t>1. Enter a password
+2. Verify characters are masked</t>
+  </si>
+  <si>
+    <t>Password input should be hidden behind dots or asterisks</t>
+  </si>
+  <si>
+    <t>Verify Special Characters Allowed in Password</t>
+  </si>
+  <si>
+    <t>Validation Check</t>
+  </si>
+  <si>
+    <t>1. Enter a password with special characters
+2. Click 'Continue'</t>
+  </si>
+  <si>
+    <t>Password should be accepted if it meets security criteria</t>
+  </si>
+  <si>
+    <t>Verify Minimum Password Length Requirement</t>
+  </si>
+  <si>
+    <t>1. Enter a password shorter than the required length
+2. Click 'Continue'</t>
+  </si>
+  <si>
+    <t>Verify Maximum Password Length Handling</t>
+  </si>
+  <si>
+    <t>1. Enter an extremely long password
+2. Click 'Continue'</t>
+  </si>
+  <si>
+    <t>Either an error is displayed, or the input is truncated</t>
+  </si>
+  <si>
+    <t>Generisch! Required length ist zu ungenau! Was ist die exakte Zahl</t>
+  </si>
+  <si>
+    <t>Generisch! Was für ein Error wird angezeigt?</t>
+  </si>
+  <si>
+    <t>Generisch was sind die Sicherheitskriterien?</t>
+  </si>
+  <si>
+    <t>Generisch! was ist die nachricht?</t>
+  </si>
+  <si>
+    <t>Generisch was ist die Error Message</t>
+  </si>
+  <si>
+    <t>(17/23)*100
+= 73,9%</t>
+  </si>
+  <si>
+    <t>(17/25)*100
+= 68%</t>
   </si>
 </sst>
 </file>
@@ -1467,7 +1739,7 @@
         <v>32</v>
       </c>
       <c r="D1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="36" x14ac:dyDescent="0.25">
@@ -1497,6 +1769,9 @@
     <row r="5" spans="1:4" ht="36" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
+      </c>
+      <c r="B5">
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" x14ac:dyDescent="0.25">
@@ -2862,11 +3137,11 @@
       <c r="G13" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="H13" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="I13" s="9">
-        <v>1</v>
+      <c r="H13" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="I13" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="90" x14ac:dyDescent="0.25">
@@ -2891,11 +3166,11 @@
       <c r="G14" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="I14" s="9">
-        <v>1</v>
+      <c r="H14" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="I14" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="90" x14ac:dyDescent="0.25">
@@ -3166,7 +3441,7 @@
       </c>
       <c r="I24" s="8">
         <f>SUM(I2:I23)</f>
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -3184,7 +3459,7 @@
         <v>144</v>
       </c>
       <c r="I26" s="18" t="s">
-        <v>262</v>
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -3568,7 +3843,7 @@
         <v>144</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -3578,9 +3853,713 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B87FF5BC-0666-433A-9ADB-FC60B68CC696}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="18.28515625" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="4" max="4" width="20.28515625" customWidth="1"/>
+    <col min="5" max="5" width="23.85546875" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="I2" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="I3" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="I4" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="I5" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="I6" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="I7" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>290</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="I8" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="I9" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="I10" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="I11" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="I12" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>308</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="I13" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>310</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="I14" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>313</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="I15" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="I16" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>318</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>319</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="I17" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>320</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>321</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>322</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="I18" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>323</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>324</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>325</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="I19" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>328</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="I20" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>331</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="I21" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>333</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="I22" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>337</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H23" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="I23" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="H24" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="I24" s="8">
+        <f>SUM(I2:I23)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="H25" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="I25" s="8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="H26" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>344</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Testdaten/Testdaten von und für GPT-4/OpenCart-TestExecution Results_GPT-4_ausgewertet.xlsx
+++ b/Testdaten/Testdaten von und für GPT-4/OpenCart-TestExecution Results_GPT-4_ausgewertet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marvi\Desktop\Bachelor-Thesis\Testdaten\Testdaten von und für GPT-4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8901C523-13D3-469C-ADEA-9FBF523136E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21354433-E533-46F3-9837-F35C38CAB860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Scenarios" sheetId="1" r:id="rId1"/>
@@ -18,32 +18,30 @@
     <sheet name="Login" sheetId="3" r:id="rId3"/>
     <sheet name="Logout" sheetId="32" r:id="rId4"/>
     <sheet name="Forgot Password" sheetId="4" r:id="rId5"/>
-    <sheet name="Search" sheetId="5" r:id="rId6"/>
-    <sheet name="Product Display Page" sheetId="6" r:id="rId7"/>
-    <sheet name="Add to Cart" sheetId="7" r:id="rId8"/>
-    <sheet name="Wish List" sheetId="8" r:id="rId9"/>
-    <sheet name="Shopping Cart" sheetId="9" r:id="rId10"/>
-    <sheet name="Home Page" sheetId="10" r:id="rId11"/>
-    <sheet name="Checkout" sheetId="11" r:id="rId12"/>
-    <sheet name="My Account" sheetId="12" r:id="rId13"/>
-    <sheet name="My Account Information" sheetId="13" r:id="rId14"/>
-    <sheet name="Change Password" sheetId="14" r:id="rId15"/>
-    <sheet name="Address Book" sheetId="15" r:id="rId16"/>
-    <sheet name="Order History" sheetId="16" r:id="rId17"/>
-    <sheet name="Order Information" sheetId="17" r:id="rId18"/>
-    <sheet name="Product Returns" sheetId="18" r:id="rId19"/>
-    <sheet name="Downloads" sheetId="19" r:id="rId20"/>
-    <sheet name="Reward Points" sheetId="20" r:id="rId21"/>
-    <sheet name="Returns" sheetId="21" r:id="rId22"/>
-    <sheet name="Transactions" sheetId="22" r:id="rId23"/>
-    <sheet name="Recurring Payments" sheetId="23" r:id="rId24"/>
-    <sheet name="Affiliate" sheetId="24" r:id="rId25"/>
-    <sheet name="Newsletter" sheetId="25" r:id="rId26"/>
-    <sheet name="Contact Us" sheetId="26" r:id="rId27"/>
-    <sheet name="Gift Certificate" sheetId="27" r:id="rId28"/>
-    <sheet name="Specail Offers" sheetId="28" r:id="rId29"/>
-    <sheet name="Header Menu Footer Options" sheetId="29" r:id="rId30"/>
-    <sheet name="Currencies" sheetId="31" r:id="rId31"/>
+    <sheet name="Add to Cart" sheetId="7" r:id="rId6"/>
+    <sheet name="Wish List" sheetId="8" r:id="rId7"/>
+    <sheet name="Shopping Cart" sheetId="9" r:id="rId8"/>
+    <sheet name="Home Page" sheetId="10" r:id="rId9"/>
+    <sheet name="Checkout" sheetId="11" r:id="rId10"/>
+    <sheet name="My Account" sheetId="12" r:id="rId11"/>
+    <sheet name="My Account Information" sheetId="13" r:id="rId12"/>
+    <sheet name="Change Password" sheetId="14" r:id="rId13"/>
+    <sheet name="Address Book" sheetId="15" r:id="rId14"/>
+    <sheet name="Order History" sheetId="16" r:id="rId15"/>
+    <sheet name="Order Information" sheetId="17" r:id="rId16"/>
+    <sheet name="Product Returns" sheetId="18" r:id="rId17"/>
+    <sheet name="Downloads" sheetId="19" r:id="rId18"/>
+    <sheet name="Reward Points" sheetId="20" r:id="rId19"/>
+    <sheet name="Returns" sheetId="21" r:id="rId20"/>
+    <sheet name="Transactions" sheetId="22" r:id="rId21"/>
+    <sheet name="Recurring Payments" sheetId="23" r:id="rId22"/>
+    <sheet name="Affiliate" sheetId="24" r:id="rId23"/>
+    <sheet name="Newsletter" sheetId="25" r:id="rId24"/>
+    <sheet name="Contact Us" sheetId="26" r:id="rId25"/>
+    <sheet name="Gift Certificate" sheetId="27" r:id="rId26"/>
+    <sheet name="Specail Offers" sheetId="28" r:id="rId27"/>
+    <sheet name="Header Menu Footer Options" sheetId="29" r:id="rId28"/>
+    <sheet name="Currencies" sheetId="31" r:id="rId29"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -66,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="379">
   <si>
     <t>Test Scenario Description</t>
   </si>
@@ -81,15 +79,6 @@
   </si>
   <si>
     <t>Validate the working of Forgot Password functionality</t>
-  </si>
-  <si>
-    <t>Validate the working of Search functionality</t>
-  </si>
-  <si>
-    <t>Validate the working of Product Compare functionality</t>
-  </si>
-  <si>
-    <t>Validate the Product Display Page functionality for the different types of Products</t>
   </si>
   <si>
     <t>Validate the working of 'Add to Cart' functionality</t>
@@ -1273,6 +1262,138 @@
   <si>
     <t>(17/25)*100
 = 68%</t>
+  </si>
+  <si>
+    <t>Search for a Product</t>
+  </si>
+  <si>
+    <t>Open the Application URL</t>
+  </si>
+  <si>
+    <t>Product Search</t>
+  </si>
+  <si>
+    <t>1. Enter 'MacBook' in the search bar
+2. Click on 'Search' button</t>
+  </si>
+  <si>
+    <t>Search results display MacBook products</t>
+  </si>
+  <si>
+    <t>Add a Product to Cart from Search Results</t>
+  </si>
+  <si>
+    <t>Add to Cart</t>
+  </si>
+  <si>
+    <t>1. Enter 'MacBook' in the search bar
+2. Click on 'Search' button
+3. Click on 'Add to Cart' button for a product in search results</t>
+  </si>
+  <si>
+    <t>Success message: 'You have added [Product] to your shopping cart!'
+Product appears in the shopping cart</t>
+  </si>
+  <si>
+    <t>Open Product Page and Add to Cart</t>
+  </si>
+  <si>
+    <t>Open the Application URL
+A product is added to Wish List page - &lt;Refer Test Data&gt;</t>
+  </si>
+  <si>
+    <t>1. Enter 'MacBook' in the search bar
+2. Click on 'Search' button
+3. Click on a product from search results
+4. Click on 'Add to Cart' button on product page</t>
+  </si>
+  <si>
+    <t>Success message: 'You have added [Product] to your shopping cart!'
+Product appears in the shopping cart
+Product should be successfully displayed in the 'Shopping Cart' page</t>
+  </si>
+  <si>
+    <t>Verify Product in Shopping Cart</t>
+  </si>
+  <si>
+    <t>Cart Validation</t>
+  </si>
+  <si>
+    <t>1. Click on 'Shopping Cart' icon
+2. Verify that the added product is listed</t>
+  </si>
+  <si>
+    <t>Product appears in the shopping cart with correct quantity and price
+Product should be successfully displayed in the 'Shopping Cart' page</t>
+  </si>
+  <si>
+    <t>Add Multiple Products to Cart</t>
+  </si>
+  <si>
+    <t>Cart Management</t>
+  </si>
+  <si>
+    <t>1. Add multiple different products to the cart
+2. Open 'Shopping Cart'</t>
+  </si>
+  <si>
+    <t>All selected products appear in the shopping cart</t>
+  </si>
+  <si>
+    <t>Increase Product Quantity in Cart</t>
+  </si>
+  <si>
+    <t>1. Go to 'Shopping Cart'
+2. Increase the quantity of a product
+3. Click update</t>
+  </si>
+  <si>
+    <t>Quantity is updated correctly, and total price reflects the change</t>
+  </si>
+  <si>
+    <t>Remove a Product from Cart</t>
+  </si>
+  <si>
+    <t>1. Go to 'Shopping Cart'
+2. Click on 'Remove' button next to a product</t>
+  </si>
+  <si>
+    <t>Product is removed from the shopping cart</t>
+  </si>
+  <si>
+    <t>Verify UI Elements in Shopping Cart</t>
+  </si>
+  <si>
+    <t>UI Validation</t>
+  </si>
+  <si>
+    <t>1. Check if the 'Checkout' button is visible
+2. Verify that subtotal, tax, and total price are displayed</t>
+  </si>
+  <si>
+    <t>All UI elements are displayed correctly
+Product should be successfully displayed in the 'Shopping Cart' page</t>
+  </si>
+  <si>
+    <t>Verify Shopping Cart Retention After Page Refresh</t>
+  </si>
+  <si>
+    <t>Session Handling</t>
+  </si>
+  <si>
+    <t>1. Refresh the page
+2. Click on 'Shopping Cart'</t>
+  </si>
+  <si>
+    <t>Product remains in the shopping cart after refresh
+Product should be successfully displayed in the 'Shopping Cart' page</t>
+  </si>
+  <si>
+    <t>Falsches Erwartetes Ergebnis. Es spielt in diese Fall keine Rolle ob das Produkt. Angezeigt wird. Es könnte auch kein Produkt da sein</t>
+  </si>
+  <si>
+    <t>(8/9)*100
+= 88,9%</t>
   </si>
 </sst>
 </file>
@@ -1377,7 +1498,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1433,6 +1554,9 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1451,8 +1575,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8C7FFBB2-7CCD-49BB-9944-D00EE224352F}" name="Tabelle1" displayName="Tabelle1" ref="A1:B33" totalsRowShown="0">
-  <autoFilter ref="A1:B33" xr:uid="{8C7FFBB2-7CCD-49BB-9944-D00EE224352F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8C7FFBB2-7CCD-49BB-9944-D00EE224352F}" name="Tabelle1" displayName="Tabelle1" ref="A1:B30" totalsRowShown="0">
+  <autoFilter ref="A1:B30" xr:uid="{8C7FFBB2-7CCD-49BB-9944-D00EE224352F}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{A2618F72-197B-499E-B52B-642A285393BE}" name="Test Scenario Description"/>
     <tableColumn id="2" xr3:uid="{EB19E503-6BD2-43AB-9D47-D977A7C81992}" name="Number of Test Cases"/>
@@ -1724,7 +1848,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="74.28515625" customWidth="1"/>
@@ -1736,10 +1860,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="36" x14ac:dyDescent="0.25">
@@ -1778,8 +1902,11 @@
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="36" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -1799,22 +1926,22 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="36" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="36" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="36" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="36" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -1859,54 +1986,39 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="36" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" ht="18" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" ht="36" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" ht="18" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
+    <row r="26" spans="1:1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+    <row r="27" spans="1:1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="5" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="4" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1918,7 +2030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69D18EF4-CB07-482B-8120-500AFEA41AAD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E3281B2-ECE2-4229-8E21-DD0154D6B597}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -1927,7 +2039,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F59ECDB-6887-412D-AE40-CAEFBBF69F30}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC891B4D-CEB7-428C-AF11-DCFCD005A99F}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -1936,7 +2048,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E3281B2-ECE2-4229-8E21-DD0154D6B597}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67FE3611-CBBC-427E-B012-E6C8579C6CA3}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -1945,7 +2057,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC891B4D-CEB7-428C-AF11-DCFCD005A99F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74085656-08C1-43DA-983A-046601A87472}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -1954,7 +2066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67FE3611-CBBC-427E-B012-E6C8579C6CA3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{884EF907-734D-47C2-A462-0A7DDD7773AA}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -1963,7 +2075,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74085656-08C1-43DA-983A-046601A87472}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8E5B671-0B83-466E-B4C9-A5B4C2F32FB0}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -1972,7 +2084,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{884EF907-734D-47C2-A462-0A7DDD7773AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAAF1EEB-08B3-4462-A935-285A740C21B1}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -1981,7 +2093,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8E5B671-0B83-466E-B4C9-A5B4C2F32FB0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB318571-7AA6-48E7-8B34-1554E4D4D71F}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -1990,7 +2102,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAAF1EEB-08B3-4462-A935-285A740C21B1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6366D9F1-B0C3-4E0E-A154-D57D8B3B5093}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -1999,7 +2111,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB318571-7AA6-48E7-8B34-1554E4D4D71F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBD04566-2B9F-4B07-AA34-BF57464EB60D}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2025,57 +2137,57 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="H1" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>38</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>46</v>
-      </c>
       <c r="G2" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I2" s="9">
         <v>1</v>
@@ -2083,28 +2195,28 @@
     </row>
     <row r="3" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>52</v>
-      </c>
       <c r="G3" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I3" s="12">
         <v>0</v>
@@ -2112,28 +2224,28 @@
     </row>
     <row r="4" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>57</v>
-      </c>
       <c r="G4" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I4" s="9">
         <v>1</v>
@@ -2141,28 +2253,28 @@
     </row>
     <row r="5" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="F5" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>62</v>
-      </c>
       <c r="G5" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="I5" s="9">
         <v>1</v>
@@ -2170,28 +2282,28 @@
     </row>
     <row r="6" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="F6" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>67</v>
-      </c>
       <c r="G6" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I6" s="9">
         <v>1</v>
@@ -2199,28 +2311,28 @@
     </row>
     <row r="7" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="F7" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>72</v>
-      </c>
       <c r="G7" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I7" s="9">
         <v>1</v>
@@ -2228,28 +2340,28 @@
     </row>
     <row r="8" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="F8" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>77</v>
-      </c>
       <c r="G8" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I8" s="12">
         <v>0</v>
@@ -2257,28 +2369,28 @@
     </row>
     <row r="9" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="F9" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>82</v>
-      </c>
       <c r="G9" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I9" s="9">
         <v>1</v>
@@ -2286,28 +2398,28 @@
     </row>
     <row r="10" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="F10" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>87</v>
-      </c>
       <c r="G10" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I10" s="9">
         <v>1</v>
@@ -2315,28 +2427,28 @@
     </row>
     <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="F11" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>92</v>
-      </c>
       <c r="G11" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I11" s="9">
         <v>1</v>
@@ -2344,28 +2456,28 @@
     </row>
     <row r="12" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="F12" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>97</v>
-      </c>
       <c r="G12" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I12" s="9">
         <v>1</v>
@@ -2373,28 +2485,28 @@
     </row>
     <row r="13" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="F13" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>102</v>
-      </c>
       <c r="G13" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I13" s="9">
         <v>1</v>
@@ -2402,28 +2514,28 @@
     </row>
     <row r="14" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E14" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="F14" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>107</v>
-      </c>
       <c r="G14" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I14" s="9">
         <v>1</v>
@@ -2431,28 +2543,28 @@
     </row>
     <row r="15" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="F15" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>112</v>
-      </c>
       <c r="G15" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I15" s="9">
         <v>1</v>
@@ -2460,28 +2572,28 @@
     </row>
     <row r="16" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="F16" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>117</v>
-      </c>
       <c r="G16" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I16" s="9">
         <v>1</v>
@@ -2489,28 +2601,28 @@
     </row>
     <row r="17" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="F17" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>122</v>
-      </c>
       <c r="G17" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="I17" s="9">
         <v>1</v>
@@ -2518,28 +2630,28 @@
     </row>
     <row r="18" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="F18" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>127</v>
-      </c>
       <c r="G18" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I18" s="9">
         <v>1</v>
@@ -2547,28 +2659,28 @@
     </row>
     <row r="19" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="F19" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>132</v>
-      </c>
       <c r="G19" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="I19" s="9">
         <v>1</v>
@@ -2576,28 +2688,28 @@
     </row>
     <row r="20" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="E20" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="F20" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>137</v>
-      </c>
       <c r="G20" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I20" s="9">
         <v>1</v>
@@ -2605,28 +2717,28 @@
     </row>
     <row r="21" spans="1:9" ht="195" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E21" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="F21" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>142</v>
-      </c>
       <c r="G21" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I21" s="12">
         <v>0</v>
@@ -2634,7 +2746,7 @@
     </row>
     <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H22" s="11" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I22" s="10">
         <f>SUM(I2:I21)</f>
@@ -2643,7 +2755,7 @@
     </row>
     <row r="23" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="H23" s="11" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I23" s="8">
         <v>27</v>
@@ -2651,10 +2763,10 @@
     </row>
     <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H24" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -2663,7 +2775,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6366D9F1-B0C3-4E0E-A154-D57D8B3B5093}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E879D26-DF42-416A-B355-648FF3505B03}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2672,7 +2784,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBD04566-2B9F-4B07-AA34-BF57464EB60D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2166216-EEEF-4E1B-B517-FAF39C77E32F}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2681,7 +2793,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E879D26-DF42-416A-B355-648FF3505B03}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3BDDD2-D55F-46D4-BF02-5AC4E8168912}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2690,7 +2802,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2166216-EEEF-4E1B-B517-FAF39C77E32F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51240DEB-4720-4744-A3E5-ABE3B15218B8}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2699,7 +2811,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3BDDD2-D55F-46D4-BF02-5AC4E8168912}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F321C8C-3303-4D7C-9741-9B98D2CB30B9}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2708,7 +2820,7 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51240DEB-4720-4744-A3E5-ABE3B15218B8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D0881DA-FFFD-4EA2-A7CE-6EEFF29BDA2D}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2717,7 +2829,7 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F321C8C-3303-4D7C-9741-9B98D2CB30B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C6C93B5-A0D8-4D55-82E6-2C662B74A26E}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2726,7 +2838,7 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D0881DA-FFFD-4EA2-A7CE-6EEFF29BDA2D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62A08BA0-82AB-40C6-AB10-9C065EBEE794}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2735,7 +2847,7 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C6C93B5-A0D8-4D55-82E6-2C662B74A26E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADC3A216-5155-4CEF-8A20-6800539D6F36}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2744,7 +2856,7 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62A08BA0-82AB-40C6-AB10-9C065EBEE794}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7665E2E6-5E9A-4EF8-B9F5-D0AC7746DA1E}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2769,57 +2881,57 @@
   <sheetData>
     <row r="1" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>38</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I2" s="9">
         <v>1</v>
@@ -2827,28 +2939,28 @@
     </row>
     <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I3" s="9">
         <v>1</v>
@@ -2856,28 +2968,28 @@
     </row>
     <row r="4" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B4" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>155</v>
-      </c>
       <c r="G4" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I4" s="9">
         <v>1</v>
@@ -2885,28 +2997,28 @@
     </row>
     <row r="5" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B5" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>159</v>
-      </c>
       <c r="G5" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I5" s="9">
         <v>1</v>
@@ -2914,28 +3026,28 @@
     </row>
     <row r="6" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I6" s="9">
         <v>1</v>
@@ -2943,28 +3055,28 @@
     </row>
     <row r="7" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I7" s="9">
         <v>1</v>
@@ -2972,28 +3084,28 @@
     </row>
     <row r="8" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I8" s="9">
         <v>1</v>
@@ -3001,28 +3113,28 @@
     </row>
     <row r="9" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I9" s="9">
         <v>1</v>
@@ -3030,28 +3142,28 @@
     </row>
     <row r="10" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B10" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>172</v>
-      </c>
       <c r="G10" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I10" s="9">
         <v>1</v>
@@ -3059,28 +3171,28 @@
     </row>
     <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B11" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>176</v>
-      </c>
       <c r="G11" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I11" s="9">
         <v>1</v>
@@ -3088,28 +3200,28 @@
     </row>
     <row r="12" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="I12" s="9">
         <v>1</v>
@@ -3117,28 +3229,28 @@
     </row>
     <row r="13" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="I13" s="12">
         <v>0</v>
@@ -3146,28 +3258,28 @@
     </row>
     <row r="14" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="I14" s="12">
         <v>0</v>
@@ -3175,28 +3287,28 @@
     </row>
     <row r="15" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B15" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="F15" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>187</v>
-      </c>
       <c r="G15" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="I15" s="9">
         <v>1</v>
@@ -3204,28 +3316,28 @@
     </row>
     <row r="16" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B16" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="F16" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>191</v>
-      </c>
       <c r="G16" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="I16" s="9">
         <v>1</v>
@@ -3233,28 +3345,28 @@
     </row>
     <row r="17" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B17" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="F17" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>195</v>
-      </c>
       <c r="G17" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I17" s="12">
         <v>0</v>
@@ -3262,28 +3374,28 @@
     </row>
     <row r="18" spans="1:9" ht="150" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I18" s="12">
         <v>0</v>
@@ -3291,28 +3403,28 @@
     </row>
     <row r="19" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I19" s="12">
         <v>0</v>
@@ -3320,28 +3432,28 @@
     </row>
     <row r="20" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I20" s="9">
         <v>1</v>
@@ -3349,28 +3461,28 @@
     </row>
     <row r="21" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I21" s="9">
         <v>1</v>
@@ -3378,28 +3490,28 @@
     </row>
     <row r="22" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="E22" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="F22" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>209</v>
-      </c>
       <c r="G22" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I22" s="9">
         <v>1</v>
@@ -3407,28 +3519,28 @@
     </row>
     <row r="23" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="F23" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="E23" s="8" t="s">
+      <c r="G23" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H23" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>215</v>
       </c>
       <c r="I23" s="9">
         <v>1</v>
@@ -3437,7 +3549,7 @@
     <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G24" s="11"/>
       <c r="H24" s="8" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I24" s="8">
         <f>SUM(I2:I23)</f>
@@ -3447,7 +3559,7 @@
     <row r="25" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G25" s="11"/>
       <c r="H25" s="8" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I25" s="8">
         <v>23</v>
@@ -3456,31 +3568,13 @@
     <row r="26" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G26" s="11"/>
       <c r="H26" s="8" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I26" s="18" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADC3A216-5155-4CEF-8A20-6800539D6F36}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7665E2E6-5E9A-4EF8-B9F5-D0AC7746DA1E}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3503,57 +3597,57 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>38</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B2" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="E2" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="F2" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>228</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>230</v>
-      </c>
       <c r="G2" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I2" s="9">
         <v>1</v>
@@ -3561,28 +3655,28 @@
     </row>
     <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B3" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="F3" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="C3" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>234</v>
-      </c>
       <c r="G3" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="I3" s="17">
         <v>0</v>
@@ -3590,28 +3684,28 @@
     </row>
     <row r="4" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I4" s="9">
         <v>1</v>
@@ -3619,28 +3713,28 @@
     </row>
     <row r="5" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I5" s="9">
         <v>1</v>
@@ -3648,28 +3742,28 @@
     </row>
     <row r="6" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I6" s="9">
         <v>1</v>
@@ -3677,28 +3771,28 @@
     </row>
     <row r="7" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B7" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="F7" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>244</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>245</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>246</v>
-      </c>
       <c r="G7" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I7" s="9">
         <v>1</v>
@@ -3706,28 +3800,28 @@
     </row>
     <row r="8" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B8" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="F8" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="C8" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>250</v>
-      </c>
       <c r="G8" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I8" s="9">
         <v>1</v>
@@ -3735,28 +3829,28 @@
     </row>
     <row r="9" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B9" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="F9" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="C9" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>252</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>254</v>
-      </c>
       <c r="G9" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I9" s="9">
         <v>1</v>
@@ -3764,28 +3858,28 @@
     </row>
     <row r="10" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I10" s="9">
         <v>1</v>
@@ -3793,28 +3887,28 @@
     </row>
     <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I11" s="9">
         <v>1</v>
@@ -3823,7 +3917,7 @@
     <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G12" s="8"/>
       <c r="H12" s="8" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I12" s="8">
         <f>SUM(I2:I11)</f>
@@ -3832,7 +3926,7 @@
     </row>
     <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H13" s="8" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I13" s="8">
         <v>11</v>
@@ -3840,10 +3934,10 @@
     </row>
     <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H14" s="8" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -3869,57 +3963,57 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>38</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B2" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="E2" s="14" t="s">
         <v>264</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="F2" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>266</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>267</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>268</v>
-      </c>
       <c r="G2" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I2" s="9">
         <v>1</v>
@@ -3927,28 +4021,28 @@
     </row>
     <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B3" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="E3" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="F3" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="D3" s="14" t="s">
-        <v>271</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>272</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>273</v>
-      </c>
       <c r="G3" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I3" s="9">
         <v>1</v>
@@ -3956,28 +4050,28 @@
     </row>
     <row r="4" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C4" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="F4" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="D4" s="14" t="s">
-        <v>271</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>275</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>273</v>
-      </c>
       <c r="G4" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I4" s="9">
         <v>1</v>
@@ -3985,28 +4079,28 @@
     </row>
     <row r="5" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B5" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="E5" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="F5" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="D5" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>279</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>280</v>
-      </c>
       <c r="G5" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I5" s="9">
         <v>1</v>
@@ -4014,28 +4108,28 @@
     </row>
     <row r="6" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B6" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="F6" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="C6" s="14" t="s">
-        <v>277</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>282</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>284</v>
-      </c>
       <c r="G6" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I6" s="9">
         <v>1</v>
@@ -4043,28 +4137,28 @@
     </row>
     <row r="7" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B7" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="E7" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="F7" s="14" t="s">
         <v>286</v>
       </c>
-      <c r="D7" s="14" t="s">
-        <v>287</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>288</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>289</v>
-      </c>
       <c r="G7" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="I7" s="9">
         <v>1</v>
@@ -4072,28 +4166,28 @@
     </row>
     <row r="8" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B8" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="F8" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="C8" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>291</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>293</v>
-      </c>
       <c r="G8" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="I8" s="9">
         <v>1</v>
@@ -4101,28 +4195,28 @@
     </row>
     <row r="9" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="I9" s="12">
         <v>0</v>
@@ -4130,28 +4224,28 @@
     </row>
     <row r="10" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I10" s="9">
         <v>1</v>
@@ -4159,28 +4253,28 @@
     </row>
     <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I11" s="9">
         <v>1</v>
@@ -4188,28 +4282,28 @@
     </row>
     <row r="12" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I12" s="9">
         <v>1</v>
@@ -4217,28 +4311,28 @@
     </row>
     <row r="13" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I13" s="9">
         <v>1</v>
@@ -4246,28 +4340,28 @@
     </row>
     <row r="14" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I14" s="9">
         <v>1</v>
@@ -4275,28 +4369,28 @@
     </row>
     <row r="15" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B15" s="14" t="s">
+        <v>308</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>310</v>
+      </c>
+      <c r="F15" s="14" t="s">
         <v>311</v>
       </c>
-      <c r="C15" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>312</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>313</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>314</v>
-      </c>
       <c r="G15" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I15" s="9">
         <v>1</v>
@@ -4304,28 +4398,28 @@
     </row>
     <row r="16" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I16" s="9">
         <v>1</v>
@@ -4333,28 +4427,28 @@
     </row>
     <row r="17" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I17" s="12">
         <v>0</v>
@@ -4362,28 +4456,28 @@
     </row>
     <row r="18" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I18" s="9">
         <v>1</v>
@@ -4391,28 +4485,28 @@
     </row>
     <row r="19" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C19" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>321</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>322</v>
+      </c>
+      <c r="F19" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="D19" s="14" t="s">
-        <v>324</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>325</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>273</v>
-      </c>
       <c r="G19" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I19" s="9">
         <v>1</v>
@@ -4420,28 +4514,28 @@
     </row>
     <row r="20" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I20" s="9">
         <v>1</v>
@@ -4449,28 +4543,28 @@
     </row>
     <row r="21" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B21" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>328</v>
+      </c>
+      <c r="F21" s="14" t="s">
         <v>329</v>
       </c>
-      <c r="C21" s="14" t="s">
-        <v>307</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>330</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>331</v>
-      </c>
-      <c r="F21" s="14" t="s">
-        <v>332</v>
-      </c>
       <c r="G21" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="I21" s="12">
         <v>0</v>
@@ -4478,28 +4572,28 @@
     </row>
     <row r="22" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="I22" s="12">
         <v>0</v>
@@ -4507,28 +4601,28 @@
     </row>
     <row r="23" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E23" s="14" t="s">
+        <v>333</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H23" s="12" t="s">
         <v>336</v>
-      </c>
-      <c r="F23" s="14" t="s">
-        <v>337</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H23" s="12" t="s">
-        <v>339</v>
       </c>
       <c r="I23" s="12">
         <v>0</v>
@@ -4536,7 +4630,7 @@
     </row>
     <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H24" s="8" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I24" s="8">
         <f>SUM(I2:I23)</f>
@@ -4545,7 +4639,7 @@
     </row>
     <row r="25" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H25" s="8" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I25" s="8">
         <v>25</v>
@@ -4553,10 +4647,10 @@
     </row>
     <row r="26" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H26" s="8" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -4565,16 +4659,345 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACCF51F9-3319-459B-87DB-F023A541C9C3}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8819886F-B11A-44ED-87B0-0DB3C124ED3B}">
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+    <col min="8" max="8" width="19.5703125" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>344</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>345</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>346</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="I2" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="135" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>347</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>348</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>349</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>350</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="I3" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="165" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>352</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>348</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="I4" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>357</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>358</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="I5" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>359</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>360</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>361</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="I6" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>360</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>365</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="I7" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>360</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>368</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="I8" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>369</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>370</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>371</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>372</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="I9" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>373</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>374</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>376</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="I10" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="G11" s="10"/>
+      <c r="H11" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="I11" s="10">
+        <f>SUM(I2:I10)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="G12" s="10"/>
+      <c r="H12" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="I12" s="10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="G13" s="10"/>
+      <c r="H13" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>378</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF293EA0-B5E7-4CA4-88EA-BB5093B9A174}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0C77B75-3DB4-41BB-A87D-FCE0B7306371}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -4583,7 +5006,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8819886F-B11A-44ED-87B0-0DB3C124ED3B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69D18EF4-CB07-482B-8120-500AFEA41AAD}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -4592,7 +5015,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0C77B75-3DB4-41BB-A87D-FCE0B7306371}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F59ECDB-6887-412D-AE40-CAEFBBF69F30}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/Testdaten/Testdaten von und für GPT-4/OpenCart-TestExecution Results_GPT-4_ausgewertet.xlsx
+++ b/Testdaten/Testdaten von und für GPT-4/OpenCart-TestExecution Results_GPT-4_ausgewertet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marvi\Desktop\Bachelor-Thesis\Testdaten\Testdaten von und für GPT-4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DCA4BCD-51DD-4B4B-AB40-AEEFC5F1C2F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A29C9E1-8209-4130-8EB9-42A44FFABC26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,29 +19,25 @@
     <sheet name="Logout" sheetId="32" r:id="rId4"/>
     <sheet name="Forgot Password" sheetId="4" r:id="rId5"/>
     <sheet name="Add to Cart" sheetId="7" r:id="rId6"/>
-    <sheet name="Wish List" sheetId="8" r:id="rId7"/>
-    <sheet name="Shopping Cart" sheetId="9" r:id="rId8"/>
-    <sheet name="Home Page" sheetId="10" r:id="rId9"/>
-    <sheet name="Checkout" sheetId="11" r:id="rId10"/>
-    <sheet name="My Account" sheetId="12" r:id="rId11"/>
-    <sheet name="My Account Information" sheetId="13" r:id="rId12"/>
-    <sheet name="Change Password" sheetId="14" r:id="rId13"/>
-    <sheet name="Address Book" sheetId="15" r:id="rId14"/>
-    <sheet name="Order History" sheetId="16" r:id="rId15"/>
-    <sheet name="Order Information" sheetId="17" r:id="rId16"/>
-    <sheet name="Product Returns" sheetId="18" r:id="rId17"/>
-    <sheet name="Downloads" sheetId="19" r:id="rId18"/>
-    <sheet name="Reward Points" sheetId="20" r:id="rId19"/>
-    <sheet name="Returns" sheetId="21" r:id="rId20"/>
-    <sheet name="Transactions" sheetId="22" r:id="rId21"/>
-    <sheet name="Recurring Payments" sheetId="23" r:id="rId22"/>
-    <sheet name="Affiliate" sheetId="24" r:id="rId23"/>
-    <sheet name="Newsletter" sheetId="25" r:id="rId24"/>
-    <sheet name="Contact Us" sheetId="26" r:id="rId25"/>
-    <sheet name="Gift Certificate" sheetId="27" r:id="rId26"/>
-    <sheet name="Specail Offers" sheetId="28" r:id="rId27"/>
-    <sheet name="Header Menu Footer Options" sheetId="29" r:id="rId28"/>
-    <sheet name="Currencies" sheetId="31" r:id="rId29"/>
+    <sheet name="My Account" sheetId="12" r:id="rId7"/>
+    <sheet name="My Account Information" sheetId="13" r:id="rId8"/>
+    <sheet name="Change Password" sheetId="14" r:id="rId9"/>
+    <sheet name="Address Book" sheetId="15" r:id="rId10"/>
+    <sheet name="Order History" sheetId="16" r:id="rId11"/>
+    <sheet name="Order Information" sheetId="17" r:id="rId12"/>
+    <sheet name="Product Returns" sheetId="18" r:id="rId13"/>
+    <sheet name="Downloads" sheetId="19" r:id="rId14"/>
+    <sheet name="Reward Points" sheetId="20" r:id="rId15"/>
+    <sheet name="Returns" sheetId="21" r:id="rId16"/>
+    <sheet name="Transactions" sheetId="22" r:id="rId17"/>
+    <sheet name="Recurring Payments" sheetId="23" r:id="rId18"/>
+    <sheet name="Affiliate" sheetId="24" r:id="rId19"/>
+    <sheet name="Newsletter" sheetId="25" r:id="rId20"/>
+    <sheet name="Contact Us" sheetId="26" r:id="rId21"/>
+    <sheet name="Gift Certificate" sheetId="27" r:id="rId22"/>
+    <sheet name="Specail Offers" sheetId="28" r:id="rId23"/>
+    <sheet name="Header Menu Footer Options" sheetId="29" r:id="rId24"/>
+    <sheet name="Currencies" sheetId="31" r:id="rId25"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -64,19 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="385">
-  <si>
-    <t>Validate the working of 'Wish List' functionality</t>
-  </si>
-  <si>
-    <t>Validate the working of 'Shopping Cart' functionality</t>
-  </si>
-  <si>
-    <t>Validate the working of Home Page functionality</t>
-  </si>
-  <si>
-    <t>Verifty the working of Checkout functionality</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="421">
   <si>
     <t>Validate the My Account functionality</t>
   </si>
@@ -1416,6 +1400,140 @@
   </si>
   <si>
     <t>Currencies</t>
+  </si>
+  <si>
+    <t>Modify Profile Picture</t>
+  </si>
+  <si>
+    <t>Verify Notification Preferences</t>
+  </si>
+  <si>
+    <t>Login to OpenCart</t>
+  </si>
+  <si>
+    <t>User Login</t>
+  </si>
+  <si>
+    <t>1. Click on 'Login' button
+2. Enter valid Email and Password
+3. Click 'Login' button</t>
+  </si>
+  <si>
+    <t>User is successfully logged in and redirected to the account page</t>
+  </si>
+  <si>
+    <t>Navigate to My Account</t>
+  </si>
+  <si>
+    <t>User is logged in</t>
+  </si>
+  <si>
+    <t>Account Navigation</t>
+  </si>
+  <si>
+    <t>1. Click on 'Account' button
+2. Click on 'Account Details'</t>
+  </si>
+  <si>
+    <t>User is navigated to the Account Details page</t>
+  </si>
+  <si>
+    <t>Verify Account Details Page</t>
+  </si>
+  <si>
+    <t>User is on Account Details page</t>
+  </si>
+  <si>
+    <t>1. Verify all fields are visible (Username, First Name, Last Name, Email, etc.)
+2. Verify Profile Picture section is visible
+3. Verify Submit and Cancel buttons are present</t>
+  </si>
+  <si>
+    <t>All elements are correctly displayed on the Account Details page</t>
+  </si>
+  <si>
+    <t>Update Account Information</t>
+  </si>
+  <si>
+    <t>Modify Account Data</t>
+  </si>
+  <si>
+    <t>1. Modify First Name and Last Name fields
+2. Click 'Submit' button</t>
+  </si>
+  <si>
+    <t>Success message: 'Your account details have been successfully updated!'</t>
+  </si>
+  <si>
+    <t>Verify Error for Duplicate Username</t>
+  </si>
+  <si>
+    <t>1. Enter an already registered username
+2. Click 'Submit' button</t>
+  </si>
+  <si>
+    <t>Error message: 'Username is already registered!'</t>
+  </si>
+  <si>
+    <t>Verify Error for Empty Required Fields</t>
+  </si>
+  <si>
+    <t>1. Clear First Name and Last Name fields
+2. Click 'Submit' button</t>
+  </si>
+  <si>
+    <t>Error message: 'First Name must be between 1 and 32 characters!'</t>
+  </si>
+  <si>
+    <t>Verify Profile Picture Upload</t>
+  </si>
+  <si>
+    <t>1. Click 'Browse' button under Profile Picture
+2. Select an image file
+3. Click 'Submit' button</t>
+  </si>
+  <si>
+    <t>Profile picture is successfully updated</t>
+  </si>
+  <si>
+    <t>Modify Preferences</t>
+  </si>
+  <si>
+    <t>1. Select 'Yes' for Notify Extension Updates
+2. Click 'Submit' button</t>
+  </si>
+  <si>
+    <t>Notification preference is successfully updated</t>
+  </si>
+  <si>
+    <t>Navigate via Dashboard</t>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>1. Click 'Dashboard' button
+2. Click 'Account Details'</t>
+  </si>
+  <si>
+    <t>Successful Account Update</t>
+  </si>
+  <si>
+    <t>Update Account Details</t>
+  </si>
+  <si>
+    <t>1. Modify any field with valid data
+2. Click 'Submit' button</t>
+  </si>
+  <si>
+    <t>Falsch! Etc. ein Testfall nennt alle Felder und nicht etc.</t>
+  </si>
+  <si>
+    <t>Es fehlt die Error message für Last Name</t>
+  </si>
+  <si>
+    <t>(8/13)*100
+= 61,5%</t>
   </si>
 </sst>
 </file>
@@ -1582,12 +1700,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -1600,6 +1712,12 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
@@ -1616,11 +1734,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E7F2BEDD-E806-43D3-8505-12EAAAE9CC42}" name="Tabelle1" displayName="Tabelle1" ref="A1:B26" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
-  <autoFilter ref="A1:B26" xr:uid="{E7F2BEDD-E806-43D3-8505-12EAAAE9CC42}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E7F2BEDD-E806-43D3-8505-12EAAAE9CC42}" name="Tabelle1" displayName="Tabelle1" ref="A1:B22" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
+  <autoFilter ref="A1:B22" xr:uid="{E7F2BEDD-E806-43D3-8505-12EAAAE9CC42}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{864D606B-93C4-4F0A-8037-1114AF469597}" name="Test Szenario auf Open Cart" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{201C25FB-195B-4F56-8A72-5E70DDDF2E9B}" name="Number of Test Cases" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{864D606B-93C4-4F0A-8037-1114AF469597}" name="Test Szenario auf Open Cart" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{201C25FB-195B-4F56-8A72-5E70DDDF2E9B}" name="Number of Test Cases" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1889,7 +2007,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D094905A-5468-4F97-B712-0809D4979503}">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.5703125" customWidth="1"/>
@@ -1898,15 +2016,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B2" s="5">
         <v>20</v>
@@ -1914,7 +2032,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B3" s="5">
         <v>22</v>
@@ -1922,7 +2040,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B4" s="5">
         <v>10</v>
@@ -1930,7 +2048,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B5" s="5">
         <v>22</v>
@@ -1938,7 +2056,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B6" s="5">
         <v>9</v>
@@ -1950,25 +2068,27 @@
       </c>
       <c r="B7" s="5"/>
     </row>
-    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="5"/>
-    </row>
-    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B8" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
         <v>2</v>
       </c>
       <c r="B9" s="5"/>
     </row>
-    <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="5"/>
     </row>
-    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>4</v>
       </c>
@@ -2016,53 +2136,29 @@
       </c>
       <c r="B18" s="5"/>
     </row>
-    <row r="19" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
         <v>12</v>
       </c>
       <c r="B19" s="5"/>
     </row>
-    <row r="20" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>13</v>
       </c>
       <c r="B20" s="5"/>
     </row>
     <row r="21" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="16" t="s">
         <v>14</v>
       </c>
       <c r="B21" s="5"/>
     </row>
-    <row r="22" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" s="5"/>
-    </row>
-    <row r="23" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B23" s="5"/>
-    </row>
-    <row r="24" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B24" s="5"/>
-    </row>
-    <row r="25" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A25" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B25" s="5"/>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="17" t="s">
-        <v>384</v>
-      </c>
-      <c r="B26" s="5">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="B22" s="5">
         <v>3</v>
       </c>
     </row>
@@ -2075,7 +2171,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E3281B2-ECE2-4229-8E21-DD0154D6B597}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{884EF907-734D-47C2-A462-0A7DDD7773AA}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2084,7 +2180,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC891B4D-CEB7-428C-AF11-DCFCD005A99F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8E5B671-0B83-466E-B4C9-A5B4C2F32FB0}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2093,7 +2189,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67FE3611-CBBC-427E-B012-E6C8579C6CA3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAAF1EEB-08B3-4462-A935-285A740C21B1}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2102,7 +2198,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74085656-08C1-43DA-983A-046601A87472}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB318571-7AA6-48E7-8B34-1554E4D4D71F}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2111,7 +2207,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{884EF907-734D-47C2-A462-0A7DDD7773AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6366D9F1-B0C3-4E0E-A154-D57D8B3B5093}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2120,7 +2216,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8E5B671-0B83-466E-B4C9-A5B4C2F32FB0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBD04566-2B9F-4B07-AA34-BF57464EB60D}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2129,7 +2225,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAAF1EEB-08B3-4462-A935-285A740C21B1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E879D26-DF42-416A-B355-648FF3505B03}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2138,7 +2234,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB318571-7AA6-48E7-8B34-1554E4D4D71F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2166216-EEEF-4E1B-B517-FAF39C77E32F}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2147,7 +2243,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6366D9F1-B0C3-4E0E-A154-D57D8B3B5093}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3BDDD2-D55F-46D4-BF02-5AC4E8168912}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2156,7 +2252,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBD04566-2B9F-4B07-AA34-BF57464EB60D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51240DEB-4720-4744-A3E5-ABE3B15218B8}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2182,57 +2278,57 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="G2" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="I2" s="4">
         <v>1</v>
@@ -2240,28 +2336,28 @@
     </row>
     <row r="3" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="G3" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="I3" s="7">
         <v>0</v>
@@ -2269,28 +2365,28 @@
     </row>
     <row r="4" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="G4" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I4" s="4">
         <v>1</v>
@@ -2298,28 +2394,28 @@
     </row>
     <row r="5" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="G5" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="I5" s="4">
         <v>1</v>
@@ -2327,28 +2423,28 @@
     </row>
     <row r="6" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G6" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I6" s="4">
         <v>1</v>
@@ -2356,28 +2452,28 @@
     </row>
     <row r="7" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="G7" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I7" s="4">
         <v>1</v>
@@ -2385,28 +2481,28 @@
     </row>
     <row r="8" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="G8" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="I8" s="7">
         <v>0</v>
@@ -2414,28 +2510,28 @@
     </row>
     <row r="9" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="G9" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I9" s="4">
         <v>1</v>
@@ -2443,28 +2539,28 @@
     </row>
     <row r="10" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="G10" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I10" s="4">
         <v>1</v>
@@ -2472,28 +2568,28 @@
     </row>
     <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="G11" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I11" s="4">
         <v>1</v>
@@ -2501,28 +2597,28 @@
     </row>
     <row r="12" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="G12" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I12" s="4">
         <v>1</v>
@@ -2530,28 +2626,28 @@
     </row>
     <row r="13" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="G13" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I13" s="4">
         <v>1</v>
@@ -2559,28 +2655,28 @@
     </row>
     <row r="14" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="G14" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I14" s="4">
         <v>1</v>
@@ -2588,28 +2684,28 @@
     </row>
     <row r="15" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="G15" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I15" s="4">
         <v>1</v>
@@ -2617,28 +2713,28 @@
     </row>
     <row r="16" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="G16" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I16" s="4">
         <v>1</v>
@@ -2646,28 +2742,28 @@
     </row>
     <row r="17" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="G17" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="I17" s="4">
         <v>1</v>
@@ -2675,28 +2771,28 @@
     </row>
     <row r="18" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="G18" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I18" s="4">
         <v>1</v>
@@ -2704,28 +2800,28 @@
     </row>
     <row r="19" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>119</v>
-      </c>
       <c r="G19" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I19" s="4">
         <v>1</v>
@@ -2733,28 +2829,28 @@
     </row>
     <row r="20" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="G20" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I20" s="4">
         <v>1</v>
@@ -2762,28 +2858,28 @@
     </row>
     <row r="21" spans="1:9" ht="195" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="G21" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="I21" s="7">
         <v>0</v>
@@ -2791,7 +2887,7 @@
     </row>
     <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H22" s="6" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="I22" s="5">
         <f>SUM(I2:I21)</f>
@@ -2800,7 +2896,7 @@
     </row>
     <row r="23" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="H23" s="6" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I23" s="3">
         <v>27</v>
@@ -2808,10 +2904,10 @@
     </row>
     <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H24" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -2820,7 +2916,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E879D26-DF42-416A-B355-648FF3505B03}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F321C8C-3303-4D7C-9741-9B98D2CB30B9}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2829,7 +2925,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2166216-EEEF-4E1B-B517-FAF39C77E32F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D0881DA-FFFD-4EA2-A7CE-6EEFF29BDA2D}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2838,7 +2934,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3BDDD2-D55F-46D4-BF02-5AC4E8168912}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C6C93B5-A0D8-4D55-82E6-2C662B74A26E}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2847,7 +2943,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51240DEB-4720-4744-A3E5-ABE3B15218B8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62A08BA0-82AB-40C6-AB10-9C065EBEE794}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2856,7 +2952,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F321C8C-3303-4D7C-9741-9B98D2CB30B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADC3A216-5155-4CEF-8A20-6800539D6F36}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2865,42 +2961,6 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D0881DA-FFFD-4EA2-A7CE-6EEFF29BDA2D}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C6C93B5-A0D8-4D55-82E6-2C662B74A26E}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62A08BA0-82AB-40C6-AB10-9C065EBEE794}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADC3A216-5155-4CEF-8A20-6800539D6F36}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7665E2E6-5E9A-4EF8-B9F5-D0AC7746DA1E}">
   <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2918,57 +2978,57 @@
   <sheetData>
     <row r="1" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I2" s="4">
         <v>1</v>
@@ -2976,28 +3036,28 @@
     </row>
     <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>373</v>
-      </c>
       <c r="F3" s="3" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I3" s="4">
         <v>1</v>
@@ -3005,28 +3065,28 @@
     </row>
     <row r="4" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I4" s="4">
         <v>1</v>
@@ -3034,7 +3094,7 @@
     </row>
     <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H5" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="I5" s="5">
         <f>SUM(I2:I4)</f>
@@ -3043,7 +3103,7 @@
     </row>
     <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H6" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I6" s="5">
         <v>3</v>
@@ -3051,10 +3111,10 @@
     </row>
     <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H7" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -3079,57 +3139,57 @@
   <sheetData>
     <row r="1" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="I2" s="4">
         <v>1</v>
@@ -3137,28 +3197,28 @@
     </row>
     <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I3" s="4">
         <v>1</v>
@@ -3166,28 +3226,28 @@
     </row>
     <row r="4" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I4" s="4">
         <v>1</v>
@@ -3195,28 +3255,28 @@
     </row>
     <row r="5" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I5" s="4">
         <v>1</v>
@@ -3224,28 +3284,28 @@
     </row>
     <row r="6" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="F6" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I6" s="4">
         <v>1</v>
@@ -3253,28 +3313,28 @@
     </row>
     <row r="7" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I7" s="4">
         <v>1</v>
@@ -3282,28 +3342,28 @@
     </row>
     <row r="8" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I8" s="4">
         <v>1</v>
@@ -3311,28 +3371,28 @@
     </row>
     <row r="9" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I9" s="4">
         <v>1</v>
@@ -3340,28 +3400,28 @@
     </row>
     <row r="10" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I10" s="4">
         <v>1</v>
@@ -3369,28 +3429,28 @@
     </row>
     <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I11" s="4">
         <v>1</v>
@@ -3398,28 +3458,28 @@
     </row>
     <row r="12" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I12" s="4">
         <v>1</v>
@@ -3427,28 +3487,28 @@
     </row>
     <row r="13" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="I13" s="7">
         <v>0</v>
@@ -3456,28 +3516,28 @@
     </row>
     <row r="14" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="I14" s="7">
         <v>0</v>
@@ -3485,28 +3545,28 @@
     </row>
     <row r="15" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I15" s="4">
         <v>1</v>
@@ -3514,28 +3574,28 @@
     </row>
     <row r="16" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I16" s="4">
         <v>1</v>
@@ -3543,28 +3603,28 @@
     </row>
     <row r="17" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I17" s="7">
         <v>0</v>
@@ -3572,28 +3632,28 @@
     </row>
     <row r="18" spans="1:9" ht="150" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>184</v>
-      </c>
       <c r="F18" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="I18" s="7">
         <v>0</v>
@@ -3601,28 +3661,28 @@
     </row>
     <row r="19" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="I19" s="7">
         <v>0</v>
@@ -3630,28 +3690,28 @@
     </row>
     <row r="20" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I20" s="4">
         <v>1</v>
@@ -3659,28 +3719,28 @@
     </row>
     <row r="21" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I21" s="4">
         <v>1</v>
@@ -3688,28 +3748,28 @@
     </row>
     <row r="22" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="G22" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I22" s="4">
         <v>1</v>
@@ -3717,28 +3777,28 @@
     </row>
     <row r="23" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H23" s="4" t="s">
         <v>198</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>202</v>
       </c>
       <c r="I23" s="4">
         <v>1</v>
@@ -3747,7 +3807,7 @@
     <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G24" s="6"/>
       <c r="H24" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="I24" s="3">
         <f>SUM(I2:I23)</f>
@@ -3757,7 +3817,7 @@
     <row r="25" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G25" s="6"/>
       <c r="H25" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I25" s="3">
         <v>23</v>
@@ -3766,10 +3826,10 @@
     <row r="26" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G26" s="6"/>
       <c r="H26" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -3795,57 +3855,57 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B2" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="F2" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>217</v>
-      </c>
       <c r="G2" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="I2" s="4">
         <v>1</v>
@@ -3853,28 +3913,28 @@
     </row>
     <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I3" s="12">
         <v>0</v>
@@ -3882,28 +3942,28 @@
     </row>
     <row r="4" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I4" s="4">
         <v>1</v>
@@ -3911,28 +3971,28 @@
     </row>
     <row r="5" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I5" s="4">
         <v>1</v>
@@ -3940,28 +4000,28 @@
     </row>
     <row r="6" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I6" s="4">
         <v>1</v>
@@ -3969,28 +4029,28 @@
     </row>
     <row r="7" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I7" s="4">
         <v>1</v>
@@ -3998,28 +4058,28 @@
     </row>
     <row r="8" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I8" s="4">
         <v>1</v>
@@ -4027,28 +4087,28 @@
     </row>
     <row r="9" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I9" s="4">
         <v>1</v>
@@ -4056,28 +4116,28 @@
     </row>
     <row r="10" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I10" s="4">
         <v>1</v>
@@ -4085,28 +4145,28 @@
     </row>
     <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I11" s="4">
         <v>1</v>
@@ -4115,7 +4175,7 @@
     <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="I12" s="3">
         <f>SUM(I2:I11)</f>
@@ -4124,7 +4184,7 @@
     </row>
     <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H13" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I13" s="3">
         <v>11</v>
@@ -4132,10 +4192,10 @@
     </row>
     <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H14" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -4161,57 +4221,57 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B2" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="F2" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>254</v>
-      </c>
       <c r="G2" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I2" s="4">
         <v>1</v>
@@ -4219,28 +4279,28 @@
     </row>
     <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B3" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>259</v>
-      </c>
       <c r="G3" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I3" s="4">
         <v>1</v>
@@ -4248,28 +4308,28 @@
     </row>
     <row r="4" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D4" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>261</v>
-      </c>
       <c r="F4" s="9" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I4" s="4">
         <v>1</v>
@@ -4277,28 +4337,28 @@
     </row>
     <row r="5" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>266</v>
-      </c>
       <c r="G5" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="I5" s="4">
         <v>1</v>
@@ -4306,28 +4366,28 @@
     </row>
     <row r="6" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="I6" s="4">
         <v>1</v>
@@ -4335,28 +4395,28 @@
     </row>
     <row r="7" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B7" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>275</v>
-      </c>
       <c r="G7" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I7" s="4">
         <v>1</v>
@@ -4364,28 +4424,28 @@
     </row>
     <row r="8" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I8" s="4">
         <v>1</v>
@@ -4393,28 +4453,28 @@
     </row>
     <row r="9" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="D9" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="E9" s="9" t="s">
-        <v>281</v>
-      </c>
       <c r="F9" s="9" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="I9" s="7">
         <v>0</v>
@@ -4422,28 +4482,28 @@
     </row>
     <row r="10" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I10" s="4">
         <v>1</v>
@@ -4451,28 +4511,28 @@
     </row>
     <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I11" s="4">
         <v>1</v>
@@ -4480,28 +4540,28 @@
     </row>
     <row r="12" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I12" s="4">
         <v>1</v>
@@ -4509,28 +4569,28 @@
     </row>
     <row r="13" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I13" s="4">
         <v>1</v>
@@ -4538,28 +4598,28 @@
     </row>
     <row r="14" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="I14" s="4">
         <v>1</v>
@@ -4567,28 +4627,28 @@
     </row>
     <row r="15" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I15" s="4">
         <v>1</v>
@@ -4596,28 +4656,28 @@
     </row>
     <row r="16" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I16" s="4">
         <v>1</v>
@@ -4625,28 +4685,28 @@
     </row>
     <row r="17" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="I17" s="7">
         <v>0</v>
@@ -4654,28 +4714,28 @@
     </row>
     <row r="18" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I18" s="4">
         <v>1</v>
@@ -4683,28 +4743,28 @@
     </row>
     <row r="19" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I19" s="4">
         <v>1</v>
@@ -4712,28 +4772,28 @@
     </row>
     <row r="20" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I20" s="4">
         <v>1</v>
@@ -4741,28 +4801,28 @@
     </row>
     <row r="21" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="I21" s="7">
         <v>0</v>
@@ -4770,28 +4830,28 @@
     </row>
     <row r="22" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D22" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="E22" s="9" t="s">
         <v>316</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="F22" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H22" s="7" t="s">
         <v>320</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>324</v>
       </c>
       <c r="I22" s="7">
         <v>0</v>
@@ -4799,28 +4859,28 @@
     </row>
     <row r="23" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B23" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H23" s="7" t="s">
         <v>321</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>316</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>323</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>325</v>
       </c>
       <c r="I23" s="7">
         <v>0</v>
@@ -4828,7 +4888,7 @@
     </row>
     <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H24" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="I24" s="3">
         <f>SUM(I2:I23)</f>
@@ -4837,7 +4897,7 @@
     </row>
     <row r="25" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H25" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I25" s="3">
         <v>25</v>
@@ -4845,10 +4905,10 @@
     </row>
     <row r="26" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H26" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -4873,57 +4933,57 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B2" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="F2" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>332</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>333</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>335</v>
-      </c>
       <c r="G2" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I2" s="4">
         <v>1</v>
@@ -4931,28 +4991,28 @@
     </row>
     <row r="3" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I3" s="14">
         <v>1</v>
@@ -4960,28 +5020,28 @@
     </row>
     <row r="4" spans="1:9" ht="165" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I4" s="14">
         <v>1</v>
@@ -4989,28 +5049,28 @@
     </row>
     <row r="5" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I5" s="14">
         <v>1</v>
@@ -5018,28 +5078,28 @@
     </row>
     <row r="6" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I6" s="14">
         <v>1</v>
@@ -5047,28 +5107,28 @@
     </row>
     <row r="7" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D7" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>353</v>
-      </c>
       <c r="F7" s="9" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I7" s="14">
         <v>1</v>
@@ -5076,28 +5136,28 @@
     </row>
     <row r="8" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I8" s="14">
         <v>1</v>
@@ -5105,28 +5165,28 @@
     </row>
     <row r="9" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="I9" s="12">
         <v>0</v>
@@ -5134,28 +5194,28 @@
     </row>
     <row r="10" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I10" s="14">
         <v>1</v>
@@ -5164,7 +5224,7 @@
     <row r="11" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G11" s="5"/>
       <c r="H11" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="I11" s="5">
         <f>SUM(I2:I10)</f>
@@ -5174,7 +5234,7 @@
     <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G12" s="5"/>
       <c r="H12" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I12" s="5">
         <v>9</v>
@@ -5183,10 +5243,10 @@
     <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G13" s="5"/>
       <c r="H13" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -5195,25 +5255,390 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0C77B75-3DB4-41BB-A87D-FCE0B7306371}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC891B4D-CEB7-428C-AF11-DCFCD005A99F}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.7109375" customWidth="1"/>
+    <col min="2" max="3" width="18.140625" customWidth="1"/>
+    <col min="4" max="5" width="17.7109375" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" customWidth="1"/>
+    <col min="7" max="7" width="18.42578125" customWidth="1"/>
+    <col min="8" max="8" width="16.7109375" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+  </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69D18EF4-CB07-482B-8120-500AFEA41AAD}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67FE3611-CBBC-427E-B012-E6C8579C6CA3}">
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="29" customWidth="1"/>
+    <col min="2" max="2" width="20.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="16.5703125" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" customWidth="1"/>
+    <col min="8" max="8" width="17.28515625" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="I2" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="I3" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="165" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="I4" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="I5" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="I6" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="I7" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="I9" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="I10" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="I11" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="H12" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="I12" s="3">
+        <f>SUM(I2:I11)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="H13" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="I13" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="H14" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>420</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F59ECDB-6887-412D-AE40-CAEFBBF69F30}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74085656-08C1-43DA-983A-046601A87472}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/Testdaten/Testdaten von und für GPT-4/OpenCart-TestExecution Results_GPT-4_ausgewertet.xlsx
+++ b/Testdaten/Testdaten von und für GPT-4/OpenCart-TestExecution Results_GPT-4_ausgewertet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marvi\Desktop\Bachelor-Thesis\Testdaten\Testdaten von und für GPT-4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A29C9E1-8209-4130-8EB9-42A44FFABC26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA3575E4-3EC9-48B7-AE7D-92139570410B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="471">
   <si>
     <t>Validate the My Account functionality</t>
   </si>
@@ -1534,6 +1534,172 @@
   <si>
     <t>(8/13)*100
 = 61,5%</t>
+  </si>
+  <si>
+    <t>Verify user can access Account Details page</t>
+  </si>
+  <si>
+    <t>Open OpenCart.com
+User is logged in</t>
+  </si>
+  <si>
+    <t>Navigation to Account Details</t>
+  </si>
+  <si>
+    <t>User should be redirected to Account Details page</t>
+  </si>
+  <si>
+    <t>Verify Account Details page displays correct user information</t>
+  </si>
+  <si>
+    <t>Check user information in Account Details</t>
+  </si>
+  <si>
+    <t>1. Navigate to 'Account Details' page
+2. Verify user information is displayed correctly</t>
+  </si>
+  <si>
+    <t>User information should be correctly displayed</t>
+  </si>
+  <si>
+    <t>Verify 'Edit My Information' page elements are visible</t>
+  </si>
+  <si>
+    <t>Verify UI elements on Edit My Information page</t>
+  </si>
+  <si>
+    <t>1. Navigate to 'Edit My Information' page
+2. Verify all UI elements are visible</t>
+  </si>
+  <si>
+    <t>All UI elements should be present and visible</t>
+  </si>
+  <si>
+    <t>Verify user can navigate to Dashboard from Account Details</t>
+  </si>
+  <si>
+    <t>Navigation from Account Details to Dashboard</t>
+  </si>
+  <si>
+    <t>1. Click on 'Dashboard' button
+2. Verify redirection to Dashboard</t>
+  </si>
+  <si>
+    <t>User should be redirected to Dashboard</t>
+  </si>
+  <si>
+    <t>Verify GUI elements in 'Account' section</t>
+  </si>
+  <si>
+    <t>UI verification for Account section</t>
+  </si>
+  <si>
+    <t>1. Open 'Account' section
+2. Verify the presence of all necessary UI elements</t>
+  </si>
+  <si>
+    <t>All necessary UI elements should be displayed</t>
+  </si>
+  <si>
+    <t>Verify Dashboard menu options are displayed correctly</t>
+  </si>
+  <si>
+    <t>Ensure all menu options are displayed</t>
+  </si>
+  <si>
+    <t>1. Open 'Dashboard'
+2. Ensure all menu options are visible and clickable</t>
+  </si>
+  <si>
+    <t>All menu options should be correctly displayed</t>
+  </si>
+  <si>
+    <t>Verify user can navigate to different sections from Dashboard</t>
+  </si>
+  <si>
+    <t>Navigation between different dashboard sections</t>
+  </si>
+  <si>
+    <t>1. Navigate to 'Dashboard'
+2. Click on different sections
+3. Verify each section opens correctly</t>
+  </si>
+  <si>
+    <t>User should be able to navigate between sections</t>
+  </si>
+  <si>
+    <t>Verify error messages when entering invalid data</t>
+  </si>
+  <si>
+    <t>Entering invalid data to check error messages</t>
+  </si>
+  <si>
+    <t>1. Enter invalid data in 'Edit My Information' fields
+2. Click 'Submit'
+3. Verify error messages are displayed</t>
+  </si>
+  <si>
+    <t>Error messages should be displayed for invalid inputs</t>
+  </si>
+  <si>
+    <t>Verify successful update of account details</t>
+  </si>
+  <si>
+    <t>Updating account details and verifying changes</t>
+  </si>
+  <si>
+    <t>1. Update account details with valid data
+2. Click 'Submit'
+3. Verify success message</t>
+  </si>
+  <si>
+    <t>Success message should be displayed, and changes should reflect</t>
+  </si>
+  <si>
+    <t>Verify successful logout from account section</t>
+  </si>
+  <si>
+    <t>Logging out successfully from the account section</t>
+  </si>
+  <si>
+    <t>1. Click on 'Logout' button
+2. Verify redirection to homepage</t>
+  </si>
+  <si>
+    <t>User should be logged out and redirected to homepage</t>
+  </si>
+  <si>
+    <t>Verify account details remain unchanged after page refresh</t>
+  </si>
+  <si>
+    <t>Checking if account details persist after refresh</t>
+  </si>
+  <si>
+    <t>1. Make changes in account details
+2. Refresh the page
+3. Verify if the changes persist</t>
+  </si>
+  <si>
+    <t>Account details should persist after page refresh</t>
+  </si>
+  <si>
+    <t>Falsch, wenn man auf das Dashboard klickt, kommt man wieder auf die My Account Seite</t>
+  </si>
+  <si>
+    <t>Es wurde nicht nach Edit Information Testfälle gefragt! Generisch, was sind die Error Messages!</t>
+  </si>
+  <si>
+    <t>Es wurde nicht nach Edit Information Testfälle gefragt! Generisch, ist success Messages!</t>
+  </si>
+  <si>
+    <t>Generisch, was sind die notwendigen UI Elemente</t>
+  </si>
+  <si>
+    <t>Generisch, was sind die UI Elemente</t>
+  </si>
+  <si>
+    <t>(4/10)*100
+= 40%</t>
   </si>
 </sst>
 </file>
@@ -2066,7 +2232,9 @@
       <c r="A7" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="5"/>
+      <c r="B7" s="5">
+        <v>11</v>
+      </c>
     </row>
     <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
@@ -5256,18 +5424,393 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC891B4D-CEB7-428C-AF11-DCFCD005A99F}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.7109375" customWidth="1"/>
-    <col min="2" max="3" width="18.140625" customWidth="1"/>
-    <col min="4" max="5" width="17.7109375" customWidth="1"/>
-    <col min="6" max="6" width="19.42578125" customWidth="1"/>
+    <col min="1" max="1" width="31.85546875" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="5" width="23.140625" customWidth="1"/>
+    <col min="6" max="6" width="22.5703125" customWidth="1"/>
     <col min="7" max="7" width="18.42578125" customWidth="1"/>
     <col min="8" max="8" width="16.7109375" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="I2" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="I3" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="I4" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="I5" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="I6" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="I7" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="I8" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="I9" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="I10" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="I11" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="I12" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="H13" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="I13" s="5">
+        <f>SUM(I2:I12)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="H14" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="I14" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="H15" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>470</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Testdaten/Testdaten von und für GPT-4/OpenCart-TestExecution Results_GPT-4_ausgewertet.xlsx
+++ b/Testdaten/Testdaten von und für GPT-4/OpenCart-TestExecution Results_GPT-4_ausgewertet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marvi\Desktop\Bachelor-Thesis\Testdaten\Testdaten von und für GPT-4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA3575E4-3EC9-48B7-AE7D-92139570410B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67FACD32-7CD4-4CDC-95F5-312CDBBD3352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Szenarien" sheetId="33" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="468">
   <si>
     <t>Validate the My Account functionality</t>
   </si>
@@ -1201,9 +1201,6 @@
     <t>Generisch was sind die Sicherheitskriterien?</t>
   </si>
   <si>
-    <t>Generisch! was ist die nachricht?</t>
-  </si>
-  <si>
     <t>Generisch was ist die Error Message</t>
   </si>
   <si>
@@ -1686,20 +1683,14 @@
     <t>Falsch, wenn man auf das Dashboard klickt, kommt man wieder auf die My Account Seite</t>
   </si>
   <si>
-    <t>Es wurde nicht nach Edit Information Testfälle gefragt! Generisch, was sind die Error Messages!</t>
-  </si>
-  <si>
-    <t>Es wurde nicht nach Edit Information Testfälle gefragt! Generisch, ist success Messages!</t>
-  </si>
-  <si>
-    <t>Generisch, was sind die notwendigen UI Elemente</t>
-  </si>
-  <si>
-    <t>Generisch, was sind die UI Elemente</t>
-  </si>
-  <si>
-    <t>(4/10)*100
-= 40%</t>
+    <t>(6/10)*100
+= 60%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es wurde nicht nach Edit Information Testfälle gefragt! </t>
+  </si>
+  <si>
+    <t>Generisch! was ist die Nachricht?</t>
   </si>
 </sst>
 </file>
@@ -2182,7 +2173,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>15</v>
@@ -2190,7 +2181,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B2" s="5">
         <v>20</v>
@@ -2198,7 +2189,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B3" s="5">
         <v>22</v>
@@ -2206,7 +2197,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B4" s="5">
         <v>10</v>
@@ -2214,7 +2205,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B5" s="5">
         <v>22</v>
@@ -2222,7 +2213,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B6" s="5">
         <v>9</v>
@@ -2324,7 +2315,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B22" s="5">
         <v>3</v>
@@ -3062,7 +3053,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H23" s="6" t="s">
         <v>126</v>
       </c>
@@ -3178,19 +3169,19 @@
         <v>25</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>366</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>367</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>30</v>
@@ -3207,19 +3198,19 @@
         <v>31</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>369</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>370</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>30</v>
@@ -3236,19 +3227,19 @@
         <v>36</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>372</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>373</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>30</v>
@@ -3282,7 +3273,7 @@
         <v>127</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -3676,7 +3667,7 @@
         <v>30</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I13" s="7">
         <v>0</v>
@@ -3705,7 +3696,7 @@
         <v>30</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I14" s="7">
         <v>0</v>
@@ -3997,7 +3988,7 @@
         <v>127</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -4874,7 +4865,7 @@
         <v>30</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>323</v>
+        <v>467</v>
       </c>
       <c r="I17" s="7">
         <v>0</v>
@@ -5076,7 +5067,7 @@
         <v>127</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -5133,19 +5124,19 @@
         <v>25</v>
       </c>
       <c r="B2" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D2" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="9" t="s">
         <v>329</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="F2" s="9" t="s">
         <v>330</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>331</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>30</v>
@@ -5162,19 +5153,19 @@
         <v>31</v>
       </c>
       <c r="B3" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="9" t="s">
         <v>334</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>335</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>30</v>
@@ -5191,19 +5182,19 @@
         <v>36</v>
       </c>
       <c r="B4" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>336</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="D4" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>337</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>333</v>
-      </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="9" t="s">
         <v>338</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>339</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>30</v>
@@ -5220,19 +5211,19 @@
         <v>41</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>340</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="9" t="s">
         <v>341</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>342</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>343</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>30</v>
@@ -5249,19 +5240,19 @@
         <v>46</v>
       </c>
       <c r="B6" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="D6" s="9" t="s">
+      <c r="E6" s="9" t="s">
         <v>345</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="F6" s="9" t="s">
         <v>346</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>347</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>30</v>
@@ -5278,19 +5269,19 @@
         <v>51</v>
       </c>
       <c r="B7" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>348</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>345</v>
-      </c>
-      <c r="E7" s="9" t="s">
+      <c r="F7" s="9" t="s">
         <v>349</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>350</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>30</v>
@@ -5307,19 +5298,19 @@
         <v>56</v>
       </c>
       <c r="B8" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>351</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>345</v>
-      </c>
-      <c r="E8" s="9" t="s">
+      <c r="F8" s="9" t="s">
         <v>352</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>353</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>30</v>
@@ -5336,25 +5327,25 @@
         <v>61</v>
       </c>
       <c r="B9" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>354</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="E9" s="9" t="s">
         <v>355</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="F9" s="9" t="s">
         <v>356</v>
       </c>
-      <c r="F9" s="9" t="s">
-        <v>357</v>
-      </c>
       <c r="G9" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I9" s="12">
         <v>0</v>
@@ -5365,19 +5356,19 @@
         <v>66</v>
       </c>
       <c r="B10" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="D10" s="9" t="s">
+      <c r="E10" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="F10" s="9" t="s">
         <v>360</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>361</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>30</v>
@@ -5414,7 +5405,7 @@
         <v>127</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -5471,19 +5462,19 @@
         <v>25</v>
       </c>
       <c r="B2" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>421</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D2" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="F2" s="9" t="s">
         <v>423</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>390</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>424</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>30</v>
@@ -5500,19 +5491,19 @@
         <v>31</v>
       </c>
       <c r="B3" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>425</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="9" t="s">
         <v>426</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="9" t="s">
         <v>427</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>428</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>30</v>
@@ -5524,33 +5515,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>36</v>
       </c>
       <c r="B4" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>429</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="D4" s="9" t="s">
+      <c r="E4" s="9" t="s">
         <v>430</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="F4" s="9" t="s">
-        <v>432</v>
-      </c>
       <c r="G4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="7" t="s">
-        <v>469</v>
-      </c>
-      <c r="I4" s="7">
-        <v>0</v>
+      <c r="H4" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="90" x14ac:dyDescent="0.25">
@@ -5558,57 +5549,57 @@
         <v>41</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>433</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="9" t="s">
         <v>434</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>435</v>
       </c>
-      <c r="F5" s="9" t="s">
-        <v>436</v>
-      </c>
       <c r="G5" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I5" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B6" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>437</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="D6" s="9" t="s">
+      <c r="E6" s="9" t="s">
         <v>438</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="F6" s="9" t="s">
         <v>439</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>440</v>
-      </c>
       <c r="G6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="7" t="s">
-        <v>468</v>
-      </c>
-      <c r="I6" s="7">
-        <v>0</v>
+      <c r="H6" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="I6" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="90" x14ac:dyDescent="0.25">
@@ -5616,25 +5607,25 @@
         <v>51</v>
       </c>
       <c r="B7" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>441</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="D7" s="9" t="s">
+      <c r="E7" s="9" t="s">
         <v>442</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="F7" s="9" t="s">
         <v>443</v>
       </c>
-      <c r="F7" s="9" t="s">
-        <v>444</v>
-      </c>
       <c r="G7" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I7" s="7">
         <v>0</v>
@@ -5645,48 +5636,48 @@
         <v>56</v>
       </c>
       <c r="B8" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>445</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="D8" s="9" t="s">
+      <c r="E8" s="9" t="s">
         <v>446</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="F8" s="9" t="s">
         <v>447</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>448</v>
-      </c>
       <c r="G8" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I8" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>61</v>
       </c>
       <c r="B9" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>449</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="E9" s="9" t="s">
         <v>450</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="F9" s="9" t="s">
         <v>451</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>452</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>30</v>
@@ -5698,30 +5689,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>66</v>
       </c>
       <c r="B10" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>453</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="D10" s="9" t="s">
+      <c r="E10" s="9" t="s">
         <v>454</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="F10" s="9" t="s">
         <v>455</v>
       </c>
-      <c r="F10" s="9" t="s">
-        <v>456</v>
-      </c>
       <c r="G10" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="I10" s="7">
         <v>0</v>
@@ -5732,19 +5723,19 @@
         <v>71</v>
       </c>
       <c r="B11" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>457</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="D11" s="9" t="s">
+      <c r="E11" s="9" t="s">
         <v>458</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="F11" s="9" t="s">
         <v>459</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>460</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>30</v>
@@ -5761,19 +5752,19 @@
         <v>76</v>
       </c>
       <c r="B12" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>461</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="D12" s="9" t="s">
+      <c r="E12" s="9" t="s">
         <v>462</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="F12" s="9" t="s">
         <v>463</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>464</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>30</v>
@@ -5791,7 +5782,7 @@
       </c>
       <c r="I13" s="5">
         <f>SUM(I2:I12)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -5807,7 +5798,7 @@
         <v>127</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
     </row>
   </sheetData>
@@ -5865,19 +5856,19 @@
         <v>25</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>385</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>386</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>30</v>
@@ -5894,19 +5885,19 @@
         <v>31</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>390</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>391</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>30</v>
@@ -5923,25 +5914,25 @@
         <v>36</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>392</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>393</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>215</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>395</v>
-      </c>
       <c r="G4" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I4" s="7">
         <v>0</v>
@@ -5952,19 +5943,19 @@
         <v>41</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>398</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>399</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>30</v>
@@ -5981,19 +5972,19 @@
         <v>46</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>312</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>401</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>402</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>30</v>
@@ -6010,25 +6001,25 @@
         <v>51</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>312</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>405</v>
-      </c>
       <c r="G7" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I7" s="7">
         <v>0</v>
@@ -6039,19 +6030,19 @@
         <v>56</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>407</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>408</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>30</v>
@@ -6068,19 +6059,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>410</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>411</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>30</v>
@@ -6097,19 +6088,19 @@
         <v>66</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>414</v>
-      </c>
       <c r="F10" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>30</v>
@@ -6126,19 +6117,19 @@
         <v>71</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>417</v>
-      </c>
       <c r="F11" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>30</v>
@@ -6172,7 +6163,7 @@
         <v>127</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
   </sheetData>
